--- a/grupos/6AEV - Estadisticos 20212.xlsx
+++ b/grupos/6AEV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="98">
   <si>
     <t>Materia</t>
   </si>
@@ -140,21 +140,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Silva Villegas Mario</t>
+  </si>
+  <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
-    <t>Silva Villegas Mario</t>
-  </si>
-  <si>
-    <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -170,148 +170,148 @@
     <t>CHAVEZ</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>LARA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>VALIENTE</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>VILLAR</t>
+  </si>
+  <si>
+    <t>MONTERO</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>EUSEBIO</t>
+  </si>
+  <si>
+    <t>LUIS ARIEL</t>
+  </si>
+  <si>
+    <t>GERARDO RAUL</t>
+  </si>
+  <si>
+    <t>JONATHAN</t>
+  </si>
+  <si>
+    <t>MARTIN</t>
+  </si>
+  <si>
+    <t>ISAAC ALESSANDRO</t>
+  </si>
+  <si>
+    <t>ALEXIS ARMANDO</t>
+  </si>
+  <si>
+    <t>AGUSTIN</t>
+  </si>
+  <si>
+    <t>SALOMON</t>
+  </si>
+  <si>
+    <t>VICTOR SAUL</t>
+  </si>
+  <si>
+    <t>ALEXIS YAIR</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>IVAN</t>
+  </si>
+  <si>
+    <t>JOSUE YAMIN</t>
+  </si>
+  <si>
+    <t>ARTURO</t>
+  </si>
+  <si>
+    <t>MONSERRAT</t>
+  </si>
+  <si>
     <t>COSCAHUA</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
     <t>ESPINOSA</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>LARA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>MEDRANO</t>
   </si>
   <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
     <t>TZOYONTLE</t>
   </si>
   <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
     <t>TZOPITL</t>
   </si>
   <si>
-    <t>VALIENTE</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>VILLAR</t>
-  </si>
-  <si>
-    <t>MONTERO</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
     <t>LOZANO</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>EUSEBIO</t>
-  </si>
-  <si>
     <t>ALMA LIZETH</t>
   </si>
   <si>
-    <t>LUIS ARIEL</t>
-  </si>
-  <si>
     <t>YASIEL</t>
   </si>
   <si>
-    <t>GERARDO RAUL</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>MARTIN</t>
-  </si>
-  <si>
-    <t>ISAAC ALESSANDRO</t>
-  </si>
-  <si>
-    <t>ALEXIS ARMANDO</t>
-  </si>
-  <si>
-    <t>AGUSTIN</t>
-  </si>
-  <si>
-    <t>SALOMON</t>
-  </si>
-  <si>
-    <t>VICTOR SAUL</t>
-  </si>
-  <si>
-    <t>ALEXIS YAIR</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
     <t>JOSE DANIEL</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>JOSUE YAMIN</t>
-  </si>
-  <si>
-    <t>ARTURO</t>
-  </si>
-  <si>
-    <t>MONSERRAT</t>
   </si>
 </sst>
 </file>
@@ -800,19 +800,19 @@
         <v>-1</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F4">
         <v>-1</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H4">
         <v>-1</v>
@@ -854,19 +854,19 @@
         <v>-1</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>-1</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -877,19 +877,19 @@
         <v>6</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F5">
         <v>8</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H5">
         <v>-1</v>
@@ -931,19 +931,19 @@
         <v>6</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X5">
         <v>8</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -957,10 +957,10 @@
         <v>-1</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -1011,10 +1011,10 @@
         <v>-1</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X6">
         <v>-1</v>
@@ -1108,19 +1108,19 @@
         <v>6</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F8">
         <v>7</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H8">
         <v>-1</v>
@@ -1162,19 +1162,19 @@
         <v>6</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X8">
         <v>7</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1185,13 +1185,13 @@
         <v>6</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F9">
         <v>6</v>
@@ -1239,13 +1239,13 @@
         <v>6</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X9">
         <v>6</v>
@@ -1265,10 +1265,10 @@
         <v>-1</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F10">
         <v>6</v>
@@ -1319,10 +1319,10 @@
         <v>-1</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X10">
         <v>6</v>
@@ -1339,13 +1339,13 @@
         <v>-1</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F11">
         <v>8</v>
@@ -1393,13 +1393,13 @@
         <v>-1</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>8</v>
@@ -1416,13 +1416,13 @@
         <v>-1</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F12">
         <v>-1</v>
@@ -1470,13 +1470,13 @@
         <v>-1</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X12">
         <v>-1</v>
@@ -1493,13 +1493,13 @@
         <v>-1</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F13">
         <v>6</v>
@@ -1547,13 +1547,13 @@
         <v>-1</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>6</v>
@@ -1570,13 +1570,13 @@
         <v>7</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F14">
         <v>6</v>
@@ -1624,13 +1624,13 @@
         <v>7</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>6</v>
@@ -1650,10 +1650,10 @@
         <v>-1</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F15">
         <v>6</v>
@@ -1704,10 +1704,10 @@
         <v>-1</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X15">
         <v>6</v>
@@ -1724,13 +1724,13 @@
         <v>-1</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F16">
         <v>-1</v>
@@ -1778,13 +1778,13 @@
         <v>-1</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X16">
         <v>-1</v>
@@ -1801,13 +1801,13 @@
         <v>-1</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F17">
         <v>6</v>
@@ -1855,13 +1855,13 @@
         <v>-1</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X17">
         <v>6</v>
@@ -1878,19 +1878,19 @@
         <v>7</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F18">
         <v>8</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H18">
         <v>-1</v>
@@ -1932,19 +1932,19 @@
         <v>7</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1955,13 +1955,13 @@
         <v>-1</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F19">
         <v>-1</v>
@@ -2009,13 +2009,13 @@
         <v>-1</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>-1</v>
@@ -2032,13 +2032,13 @@
         <v>-1</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F20">
         <v>-1</v>
@@ -2086,13 +2086,13 @@
         <v>-1</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X20">
         <v>-1</v>
@@ -2109,13 +2109,13 @@
         <v>-1</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F21">
         <v>7</v>
@@ -2163,13 +2163,13 @@
         <v>-1</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -2186,13 +2186,13 @@
         <v>-1</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F22">
         <v>-1</v>
@@ -2240,13 +2240,13 @@
         <v>-1</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X22">
         <v>-1</v>
@@ -2308,7 +2308,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>40</v>
@@ -2317,27 +2317,30 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>21.05</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
+      <c r="H2">
+        <v>7.3</v>
+      </c>
       <c r="I2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>78.95</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>41</v>
@@ -2346,27 +2349,30 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>26.32</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
+      <c r="H3">
+        <v>6.4</v>
+      </c>
       <c r="I3">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>73.68000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>42</v>
@@ -2375,56 +2381,62 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>57.89</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
+      <c r="H4">
+        <v>6.7</v>
+      </c>
       <c r="I4">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>100</v>
+        <v>42.11</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5">
         <v>19</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>21.05</v>
+      </c>
+      <c r="H5">
+        <v>6.9</v>
       </c>
       <c r="I5">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>100</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>43</v>
@@ -2433,30 +2445,30 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>26.32</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>21.05</v>
       </c>
       <c r="H6">
-        <v>6.4</v>
+        <v>6.9</v>
       </c>
       <c r="I6">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>73.68000000000001</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>44</v>
@@ -2465,25 +2477,25 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>57.89</v>
+        <v>78.95</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>6.7</v>
+        <v>7.9</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J7">
-        <v>42.11</v>
+        <v>21.05</v>
       </c>
     </row>
   </sheetData>
@@ -2493,7 +2505,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F99"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2528,16 +2540,16 @@
         <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2548,113 +2560,113 @@
         <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920045</v>
+        <v>19330051920049</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920045</v>
+        <v>19330051920049</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920045</v>
+        <v>19330051920049</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920045</v>
+        <v>19330051920049</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D7" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>19330051920046</v>
+        <v>19330051920055</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
         <v>40</v>
@@ -2662,19 +2674,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920046</v>
+        <v>19330051920057</v>
       </c>
       <c r="B9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
         <v>41</v>
@@ -2682,79 +2694,79 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>19330051920046</v>
+        <v>19330051920057</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D10" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>19330051920046</v>
+        <v>19330051920056</v>
       </c>
       <c r="B11" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C11" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>19330051920049</v>
+        <v>19330051920056</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D12" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>19330051920049</v>
+        <v>19330051920056</v>
       </c>
       <c r="B13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C13" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
         <v>40</v>
@@ -2762,39 +2774,39 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>19330051920049</v>
+        <v>18330051920022</v>
       </c>
       <c r="B14" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D14" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>19330051920049</v>
+        <v>18330051920022</v>
       </c>
       <c r="B15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D15" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s">
         <v>41</v>
@@ -2802,59 +2814,59 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>19330051920049</v>
+        <v>18330051920022</v>
       </c>
       <c r="B16" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D16" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E16" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>19330051920049</v>
+        <v>19330051920058</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>19330051920053</v>
+        <v>19330051920058</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C18" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="D18" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
         <v>40</v>
@@ -2862,39 +2874,39 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>19330051920053</v>
+        <v>19330051920059</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C19" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="D19" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>19330051920053</v>
+        <v>19330051920050</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C20" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E20" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F20" t="s">
         <v>42</v>
@@ -2902,179 +2914,179 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>19330051920053</v>
+        <v>19330051920050</v>
       </c>
       <c r="B21" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C21" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F21" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>19330051920055</v>
+        <v>19330051920050</v>
       </c>
       <c r="B22" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C22" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="D22" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E22" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>19330051920055</v>
+        <v>19330051920050</v>
       </c>
       <c r="B23" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C23" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="D23" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>19330051920055</v>
+        <v>19330051920050</v>
       </c>
       <c r="B24" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C24" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="D24" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E24" t="s">
         <v>7</v>
       </c>
       <c r="F24" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>19330051920055</v>
+        <v>19330051920050</v>
       </c>
       <c r="B25" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C25" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="D25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>19330051920057</v>
+        <v>19330051920064</v>
       </c>
       <c r="B26" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C26" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D26" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E26" t="s">
         <v>6</v>
       </c>
       <c r="F26" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>19330051920057</v>
+        <v>19330051920064</v>
       </c>
       <c r="B27" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C27" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D27" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E27" t="s">
         <v>5</v>
       </c>
       <c r="F27" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>19330051920057</v>
+        <v>19330051920064</v>
       </c>
       <c r="B28" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C28" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D28" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
       </c>
       <c r="F28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>19330051920057</v>
+        <v>19330051920067</v>
       </c>
       <c r="B29" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C29" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D29" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E29" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F29" t="s">
         <v>42</v>
@@ -3082,39 +3094,39 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>19330051920057</v>
+        <v>19330051920067</v>
       </c>
       <c r="B30" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C30" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D30" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E30" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>19330051920056</v>
+        <v>19330051920067</v>
       </c>
       <c r="B31" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C31" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D31" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E31" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F31" t="s">
         <v>40</v>
@@ -3122,59 +3134,59 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>19330051920056</v>
+        <v>19330051920068</v>
       </c>
       <c r="B32" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C32" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D32" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E32" t="s">
         <v>5</v>
       </c>
       <c r="F32" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>19330051920056</v>
+        <v>19330051920068</v>
       </c>
       <c r="B33" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C33" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D33" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E33" t="s">
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>19330051920056</v>
+        <v>19330051920074</v>
       </c>
       <c r="B34" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C34" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D34" t="s">
         <v>85</v>
       </c>
       <c r="E34" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F34" t="s">
         <v>42</v>
@@ -3182,50 +3194,50 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>19330051920056</v>
+        <v>19330051920074</v>
       </c>
       <c r="B35" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C35" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D35" t="s">
         <v>85</v>
       </c>
       <c r="E35" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F35" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>18330051920022</v>
+        <v>19330051920074</v>
       </c>
       <c r="B36" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C36" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D36" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E36" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F36" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>18330051920022</v>
+        <v>18330051920078</v>
       </c>
       <c r="B37" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C37" t="s">
         <v>71</v>
@@ -3234,18 +3246,18 @@
         <v>86</v>
       </c>
       <c r="E37" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F37" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>18330051920022</v>
+        <v>18330051920078</v>
       </c>
       <c r="B38" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C38" t="s">
         <v>71</v>
@@ -3257,15 +3269,15 @@
         <v>5</v>
       </c>
       <c r="F38" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>18330051920022</v>
+        <v>18330051920078</v>
       </c>
       <c r="B39" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C39" t="s">
         <v>71</v>
@@ -3277,1207 +3289,107 @@
         <v>10</v>
       </c>
       <c r="F39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>18330051920022</v>
+        <v>19330051920075</v>
       </c>
       <c r="B40" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C40" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D40" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E40" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F40" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>18330051920022</v>
+        <v>19330051920075</v>
       </c>
       <c r="B41" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C41" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D41" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E41" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F41" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>19330051920058</v>
+        <v>19330051920081</v>
       </c>
       <c r="B42" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C42" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="D42" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E42" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F42" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>19330051920058</v>
+        <v>19330051920081</v>
       </c>
       <c r="B43" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C43" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="D43" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E43" t="s">
         <v>5</v>
       </c>
       <c r="F43" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>19330051920058</v>
+        <v>19330051920081</v>
       </c>
       <c r="B44" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C44" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="D44" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E44" t="s">
         <v>10</v>
       </c>
       <c r="F44" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>19330051920058</v>
-      </c>
-      <c r="B45" t="s">
-        <v>56</v>
-      </c>
-      <c r="C45" t="s">
-        <v>49</v>
-      </c>
-      <c r="D45" t="s">
-        <v>87</v>
-      </c>
-      <c r="E45" t="s">
-        <v>7</v>
-      </c>
-      <c r="F45" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>19330051920058</v>
-      </c>
-      <c r="B46" t="s">
-        <v>56</v>
-      </c>
-      <c r="C46" t="s">
-        <v>49</v>
-      </c>
-      <c r="D46" t="s">
-        <v>87</v>
-      </c>
-      <c r="E46" t="s">
-        <v>8</v>
-      </c>
-      <c r="F46" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>19330051920059</v>
-      </c>
-      <c r="B47" t="s">
-        <v>56</v>
-      </c>
-      <c r="C47" t="s">
-        <v>56</v>
-      </c>
-      <c r="D47" t="s">
-        <v>88</v>
-      </c>
-      <c r="E47" t="s">
-        <v>6</v>
-      </c>
-      <c r="F47" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>19330051920059</v>
-      </c>
-      <c r="B48" t="s">
-        <v>56</v>
-      </c>
-      <c r="C48" t="s">
-        <v>56</v>
-      </c>
-      <c r="D48" t="s">
-        <v>88</v>
-      </c>
-      <c r="E48" t="s">
-        <v>10</v>
-      </c>
-      <c r="F48" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>19330051920059</v>
-      </c>
-      <c r="B49" t="s">
-        <v>56</v>
-      </c>
-      <c r="C49" t="s">
-        <v>56</v>
-      </c>
-      <c r="D49" t="s">
-        <v>88</v>
-      </c>
-      <c r="E49" t="s">
-        <v>7</v>
-      </c>
-      <c r="F49" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>19330051920059</v>
-      </c>
-      <c r="B50" t="s">
-        <v>56</v>
-      </c>
-      <c r="C50" t="s">
-        <v>56</v>
-      </c>
-      <c r="D50" t="s">
-        <v>88</v>
-      </c>
-      <c r="E50" t="s">
-        <v>8</v>
-      </c>
-      <c r="F50" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>19330051920050</v>
-      </c>
-      <c r="B51" t="s">
-        <v>57</v>
-      </c>
-      <c r="C51" t="s">
-        <v>59</v>
-      </c>
-      <c r="D51" t="s">
-        <v>89</v>
-      </c>
-      <c r="E51" t="s">
-        <v>9</v>
-      </c>
-      <c r="F51" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>19330051920050</v>
-      </c>
-      <c r="B52" t="s">
-        <v>57</v>
-      </c>
-      <c r="C52" t="s">
-        <v>59</v>
-      </c>
-      <c r="D52" t="s">
-        <v>89</v>
-      </c>
-      <c r="E52" t="s">
-        <v>6</v>
-      </c>
-      <c r="F52" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>19330051920050</v>
-      </c>
-      <c r="B53" t="s">
-        <v>57</v>
-      </c>
-      <c r="C53" t="s">
-        <v>59</v>
-      </c>
-      <c r="D53" t="s">
-        <v>89</v>
-      </c>
-      <c r="E53" t="s">
-        <v>5</v>
-      </c>
-      <c r="F53" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>19330051920050</v>
-      </c>
-      <c r="B54" t="s">
-        <v>57</v>
-      </c>
-      <c r="C54" t="s">
-        <v>59</v>
-      </c>
-      <c r="D54" t="s">
-        <v>89</v>
-      </c>
-      <c r="E54" t="s">
-        <v>10</v>
-      </c>
-      <c r="F54" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>19330051920050</v>
-      </c>
-      <c r="B55" t="s">
-        <v>57</v>
-      </c>
-      <c r="C55" t="s">
-        <v>59</v>
-      </c>
-      <c r="D55" t="s">
-        <v>89</v>
-      </c>
-      <c r="E55" t="s">
-        <v>7</v>
-      </c>
-      <c r="F55" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>19330051920050</v>
-      </c>
-      <c r="B56" t="s">
-        <v>57</v>
-      </c>
-      <c r="C56" t="s">
-        <v>59</v>
-      </c>
-      <c r="D56" t="s">
-        <v>89</v>
-      </c>
-      <c r="E56" t="s">
-        <v>8</v>
-      </c>
-      <c r="F56" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>19330051920064</v>
-      </c>
-      <c r="B57" t="s">
-        <v>58</v>
-      </c>
-      <c r="C57" t="s">
-        <v>72</v>
-      </c>
-      <c r="D57" t="s">
-        <v>90</v>
-      </c>
-      <c r="E57" t="s">
-        <v>6</v>
-      </c>
-      <c r="F57" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>19330051920064</v>
-      </c>
-      <c r="B58" t="s">
-        <v>58</v>
-      </c>
-      <c r="C58" t="s">
-        <v>72</v>
-      </c>
-      <c r="D58" t="s">
-        <v>90</v>
-      </c>
-      <c r="E58" t="s">
-        <v>5</v>
-      </c>
-      <c r="F58" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>19330051920064</v>
-      </c>
-      <c r="B59" t="s">
-        <v>58</v>
-      </c>
-      <c r="C59" t="s">
-        <v>72</v>
-      </c>
-      <c r="D59" t="s">
-        <v>90</v>
-      </c>
-      <c r="E59" t="s">
-        <v>10</v>
-      </c>
-      <c r="F59" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>19330051920064</v>
-      </c>
-      <c r="B60" t="s">
-        <v>58</v>
-      </c>
-      <c r="C60" t="s">
-        <v>72</v>
-      </c>
-      <c r="D60" t="s">
-        <v>90</v>
-      </c>
-      <c r="E60" t="s">
-        <v>7</v>
-      </c>
-      <c r="F60" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>19330051920064</v>
-      </c>
-      <c r="B61" t="s">
-        <v>58</v>
-      </c>
-      <c r="C61" t="s">
-        <v>72</v>
-      </c>
-      <c r="D61" t="s">
-        <v>90</v>
-      </c>
-      <c r="E61" t="s">
-        <v>8</v>
-      </c>
-      <c r="F61" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>19330051920067</v>
-      </c>
-      <c r="B62" t="s">
-        <v>59</v>
-      </c>
-      <c r="C62" t="s">
-        <v>73</v>
-      </c>
-      <c r="D62" t="s">
-        <v>91</v>
-      </c>
-      <c r="E62" t="s">
-        <v>9</v>
-      </c>
-      <c r="F62" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>19330051920067</v>
-      </c>
-      <c r="B63" t="s">
-        <v>59</v>
-      </c>
-      <c r="C63" t="s">
-        <v>73</v>
-      </c>
-      <c r="D63" t="s">
-        <v>91</v>
-      </c>
-      <c r="E63" t="s">
-        <v>6</v>
-      </c>
-      <c r="F63" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>19330051920067</v>
-      </c>
-      <c r="B64" t="s">
-        <v>59</v>
-      </c>
-      <c r="C64" t="s">
-        <v>73</v>
-      </c>
-      <c r="D64" t="s">
-        <v>91</v>
-      </c>
-      <c r="E64" t="s">
-        <v>5</v>
-      </c>
-      <c r="F64" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>19330051920067</v>
-      </c>
-      <c r="B65" t="s">
-        <v>59</v>
-      </c>
-      <c r="C65" t="s">
-        <v>73</v>
-      </c>
-      <c r="D65" t="s">
-        <v>91</v>
-      </c>
-      <c r="E65" t="s">
-        <v>10</v>
-      </c>
-      <c r="F65" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>19330051920067</v>
-      </c>
-      <c r="B66" t="s">
-        <v>59</v>
-      </c>
-      <c r="C66" t="s">
-        <v>73</v>
-      </c>
-      <c r="D66" t="s">
-        <v>91</v>
-      </c>
-      <c r="E66" t="s">
-        <v>7</v>
-      </c>
-      <c r="F66" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>19330051920067</v>
-      </c>
-      <c r="B67" t="s">
-        <v>59</v>
-      </c>
-      <c r="C67" t="s">
-        <v>73</v>
-      </c>
-      <c r="D67" t="s">
-        <v>91</v>
-      </c>
-      <c r="E67" t="s">
-        <v>8</v>
-      </c>
-      <c r="F67" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>19330051920068</v>
-      </c>
-      <c r="B68" t="s">
-        <v>59</v>
-      </c>
-      <c r="C68" t="s">
-        <v>74</v>
-      </c>
-      <c r="D68" t="s">
-        <v>92</v>
-      </c>
-      <c r="E68" t="s">
-        <v>6</v>
-      </c>
-      <c r="F68" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>19330051920068</v>
-      </c>
-      <c r="B69" t="s">
-        <v>59</v>
-      </c>
-      <c r="C69" t="s">
-        <v>74</v>
-      </c>
-      <c r="D69" t="s">
-        <v>92</v>
-      </c>
-      <c r="E69" t="s">
-        <v>5</v>
-      </c>
-      <c r="F69" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>19330051920068</v>
-      </c>
-      <c r="B70" t="s">
-        <v>59</v>
-      </c>
-      <c r="C70" t="s">
-        <v>74</v>
-      </c>
-      <c r="D70" t="s">
-        <v>92</v>
-      </c>
-      <c r="E70" t="s">
-        <v>10</v>
-      </c>
-      <c r="F70" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>19330051920068</v>
-      </c>
-      <c r="B71" t="s">
-        <v>59</v>
-      </c>
-      <c r="C71" t="s">
-        <v>74</v>
-      </c>
-      <c r="D71" t="s">
-        <v>92</v>
-      </c>
-      <c r="E71" t="s">
-        <v>7</v>
-      </c>
-      <c r="F71" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>19330051920068</v>
-      </c>
-      <c r="B72" t="s">
-        <v>59</v>
-      </c>
-      <c r="C72" t="s">
-        <v>74</v>
-      </c>
-      <c r="D72" t="s">
-        <v>92</v>
-      </c>
-      <c r="E72" t="s">
-        <v>8</v>
-      </c>
-      <c r="F72" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>19330051920069</v>
-      </c>
-      <c r="B73" t="s">
-        <v>60</v>
-      </c>
-      <c r="C73" t="s">
-        <v>75</v>
-      </c>
-      <c r="D73" t="s">
-        <v>93</v>
-      </c>
-      <c r="E73" t="s">
-        <v>6</v>
-      </c>
-      <c r="F73" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>19330051920069</v>
-      </c>
-      <c r="B74" t="s">
-        <v>60</v>
-      </c>
-      <c r="C74" t="s">
-        <v>75</v>
-      </c>
-      <c r="D74" t="s">
-        <v>93</v>
-      </c>
-      <c r="E74" t="s">
-        <v>10</v>
-      </c>
-      <c r="F74" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>19330051920069</v>
-      </c>
-      <c r="B75" t="s">
-        <v>60</v>
-      </c>
-      <c r="C75" t="s">
-        <v>75</v>
-      </c>
-      <c r="D75" t="s">
-        <v>93</v>
-      </c>
-      <c r="E75" t="s">
-        <v>7</v>
-      </c>
-      <c r="F75" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>19330051920069</v>
-      </c>
-      <c r="B76" t="s">
-        <v>60</v>
-      </c>
-      <c r="C76" t="s">
-        <v>75</v>
-      </c>
-      <c r="D76" t="s">
-        <v>93</v>
-      </c>
-      <c r="E76" t="s">
-        <v>8</v>
-      </c>
-      <c r="F76" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>19330051920074</v>
-      </c>
-      <c r="B77" t="s">
-        <v>61</v>
-      </c>
-      <c r="C77" t="s">
-        <v>76</v>
-      </c>
-      <c r="D77" t="s">
-        <v>94</v>
-      </c>
-      <c r="E77" t="s">
-        <v>9</v>
-      </c>
-      <c r="F77" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>19330051920074</v>
-      </c>
-      <c r="B78" t="s">
-        <v>61</v>
-      </c>
-      <c r="C78" t="s">
-        <v>76</v>
-      </c>
-      <c r="D78" t="s">
-        <v>94</v>
-      </c>
-      <c r="E78" t="s">
-        <v>6</v>
-      </c>
-      <c r="F78" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>19330051920074</v>
-      </c>
-      <c r="B79" t="s">
-        <v>61</v>
-      </c>
-      <c r="C79" t="s">
-        <v>76</v>
-      </c>
-      <c r="D79" t="s">
-        <v>94</v>
-      </c>
-      <c r="E79" t="s">
-        <v>5</v>
-      </c>
-      <c r="F79" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80">
-        <v>19330051920074</v>
-      </c>
-      <c r="B80" t="s">
-        <v>61</v>
-      </c>
-      <c r="C80" t="s">
-        <v>76</v>
-      </c>
-      <c r="D80" t="s">
-        <v>94</v>
-      </c>
-      <c r="E80" t="s">
-        <v>10</v>
-      </c>
-      <c r="F80" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
-        <v>19330051920074</v>
-      </c>
-      <c r="B81" t="s">
-        <v>61</v>
-      </c>
-      <c r="C81" t="s">
-        <v>76</v>
-      </c>
-      <c r="D81" t="s">
-        <v>94</v>
-      </c>
-      <c r="E81" t="s">
-        <v>7</v>
-      </c>
-      <c r="F81" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>19330051920074</v>
-      </c>
-      <c r="B82" t="s">
-        <v>61</v>
-      </c>
-      <c r="C82" t="s">
-        <v>76</v>
-      </c>
-      <c r="D82" t="s">
-        <v>94</v>
-      </c>
-      <c r="E82" t="s">
-        <v>8</v>
-      </c>
-      <c r="F82" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83">
-        <v>18330051920078</v>
-      </c>
-      <c r="B83" t="s">
-        <v>62</v>
-      </c>
-      <c r="C83" t="s">
-        <v>77</v>
-      </c>
-      <c r="D83" t="s">
-        <v>95</v>
-      </c>
-      <c r="E83" t="s">
-        <v>9</v>
-      </c>
-      <c r="F83" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84">
-        <v>18330051920078</v>
-      </c>
-      <c r="B84" t="s">
-        <v>62</v>
-      </c>
-      <c r="C84" t="s">
-        <v>77</v>
-      </c>
-      <c r="D84" t="s">
-        <v>95</v>
-      </c>
-      <c r="E84" t="s">
-        <v>6</v>
-      </c>
-      <c r="F84" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85">
-        <v>18330051920078</v>
-      </c>
-      <c r="B85" t="s">
-        <v>62</v>
-      </c>
-      <c r="C85" t="s">
-        <v>77</v>
-      </c>
-      <c r="D85" t="s">
-        <v>95</v>
-      </c>
-      <c r="E85" t="s">
-        <v>5</v>
-      </c>
-      <c r="F85" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86">
-        <v>18330051920078</v>
-      </c>
-      <c r="B86" t="s">
-        <v>62</v>
-      </c>
-      <c r="C86" t="s">
-        <v>77</v>
-      </c>
-      <c r="D86" t="s">
-        <v>95</v>
-      </c>
-      <c r="E86" t="s">
-        <v>10</v>
-      </c>
-      <c r="F86" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87">
-        <v>18330051920078</v>
-      </c>
-      <c r="B87" t="s">
-        <v>62</v>
-      </c>
-      <c r="C87" t="s">
-        <v>77</v>
-      </c>
-      <c r="D87" t="s">
-        <v>95</v>
-      </c>
-      <c r="E87" t="s">
-        <v>7</v>
-      </c>
-      <c r="F87" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88">
-        <v>18330051920078</v>
-      </c>
-      <c r="B88" t="s">
-        <v>62</v>
-      </c>
-      <c r="C88" t="s">
-        <v>77</v>
-      </c>
-      <c r="D88" t="s">
-        <v>95</v>
-      </c>
-      <c r="E88" t="s">
-        <v>8</v>
-      </c>
-      <c r="F88" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89">
-        <v>19330051920075</v>
-      </c>
-      <c r="B89" t="s">
-        <v>63</v>
-      </c>
-      <c r="C89" t="s">
-        <v>78</v>
-      </c>
-      <c r="D89" t="s">
-        <v>96</v>
-      </c>
-      <c r="E89" t="s">
-        <v>6</v>
-      </c>
-      <c r="F89" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90">
-        <v>19330051920075</v>
-      </c>
-      <c r="B90" t="s">
-        <v>63</v>
-      </c>
-      <c r="C90" t="s">
-        <v>78</v>
-      </c>
-      <c r="D90" t="s">
-        <v>96</v>
-      </c>
-      <c r="E90" t="s">
-        <v>5</v>
-      </c>
-      <c r="F90" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91">
-        <v>19330051920075</v>
-      </c>
-      <c r="B91" t="s">
-        <v>63</v>
-      </c>
-      <c r="C91" t="s">
-        <v>78</v>
-      </c>
-      <c r="D91" t="s">
-        <v>96</v>
-      </c>
-      <c r="E91" t="s">
-        <v>10</v>
-      </c>
-      <c r="F91" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92">
-        <v>19330051920075</v>
-      </c>
-      <c r="B92" t="s">
-        <v>63</v>
-      </c>
-      <c r="C92" t="s">
-        <v>78</v>
-      </c>
-      <c r="D92" t="s">
-        <v>96</v>
-      </c>
-      <c r="E92" t="s">
-        <v>7</v>
-      </c>
-      <c r="F92" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93">
-        <v>19330051920075</v>
-      </c>
-      <c r="B93" t="s">
-        <v>63</v>
-      </c>
-      <c r="C93" t="s">
-        <v>78</v>
-      </c>
-      <c r="D93" t="s">
-        <v>96</v>
-      </c>
-      <c r="E93" t="s">
-        <v>8</v>
-      </c>
-      <c r="F93" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94">
-        <v>19330051920081</v>
-      </c>
-      <c r="B94" t="s">
-        <v>64</v>
-      </c>
-      <c r="C94" t="s">
-        <v>63</v>
-      </c>
-      <c r="D94" t="s">
-        <v>97</v>
-      </c>
-      <c r="E94" t="s">
-        <v>9</v>
-      </c>
-      <c r="F94" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95">
-        <v>19330051920081</v>
-      </c>
-      <c r="B95" t="s">
-        <v>64</v>
-      </c>
-      <c r="C95" t="s">
-        <v>63</v>
-      </c>
-      <c r="D95" t="s">
-        <v>97</v>
-      </c>
-      <c r="E95" t="s">
-        <v>6</v>
-      </c>
-      <c r="F95" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96">
-        <v>19330051920081</v>
-      </c>
-      <c r="B96" t="s">
-        <v>64</v>
-      </c>
-      <c r="C96" t="s">
-        <v>63</v>
-      </c>
-      <c r="D96" t="s">
-        <v>97</v>
-      </c>
-      <c r="E96" t="s">
-        <v>5</v>
-      </c>
-      <c r="F96" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="A97">
-        <v>19330051920081</v>
-      </c>
-      <c r="B97" t="s">
-        <v>64</v>
-      </c>
-      <c r="C97" t="s">
-        <v>63</v>
-      </c>
-      <c r="D97" t="s">
-        <v>97</v>
-      </c>
-      <c r="E97" t="s">
-        <v>10</v>
-      </c>
-      <c r="F97" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="A98">
-        <v>19330051920081</v>
-      </c>
-      <c r="B98" t="s">
-        <v>64</v>
-      </c>
-      <c r="C98" t="s">
-        <v>63</v>
-      </c>
-      <c r="D98" t="s">
-        <v>97</v>
-      </c>
-      <c r="E98" t="s">
-        <v>7</v>
-      </c>
-      <c r="F98" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="A99">
-        <v>19330051920081</v>
-      </c>
-      <c r="B99" t="s">
-        <v>64</v>
-      </c>
-      <c r="C99" t="s">
-        <v>63</v>
-      </c>
-      <c r="D99" t="s">
-        <v>97</v>
-      </c>
-      <c r="E99" t="s">
-        <v>8</v>
-      </c>
-      <c r="F99" t="s">
-        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -4513,16 +3425,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920045</v>
+        <v>19330051920050</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E2">
         <v>6</v>
@@ -4533,186 +3445,186 @@
         <v>19330051920049</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>18330051920022</v>
+        <v>19330051920056</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920050</v>
+        <v>18330051920022</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920067</v>
+        <v>19330051920064</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920074</v>
+        <v>19330051920067</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>18330051920078</v>
+        <v>19330051920074</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D8" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E8">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920081</v>
+        <v>18330051920078</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="E9">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920057</v>
+        <v>19330051920081</v>
       </c>
       <c r="B10" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D10" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920056</v>
+        <v>19330051920045</v>
       </c>
       <c r="B11" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C11" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D11" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="E11">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920058</v>
+        <v>19330051920057</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D12" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="E12">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920064</v>
+        <v>19330051920058</v>
       </c>
       <c r="B13" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="E13">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -4720,16 +3632,16 @@
         <v>19330051920068</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D14" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -4737,84 +3649,84 @@
         <v>19330051920075</v>
       </c>
       <c r="B15" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C15" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="E15">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920046</v>
+        <v>19330051920055</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D16" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E16">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920053</v>
+        <v>19330051920059</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C17" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="D17" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E17">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920055</v>
+        <v>19330051920046</v>
       </c>
       <c r="B18" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="D18" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="E18">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920059</v>
+        <v>19330051920053</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="C19" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D19" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="E19">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -4822,16 +3734,16 @@
         <v>19330051920069</v>
       </c>
       <c r="B20" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="C20" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D20" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E20">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4841,7 +3753,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4871,6 +3783,282 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>19330051920045</v>
+      </c>
+      <c r="B2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>19330051920045</v>
+      </c>
+      <c r="B3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>19330051920057</v>
+      </c>
+      <c r="B4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>19330051920057</v>
+      </c>
+      <c r="B5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>19330051920058</v>
+      </c>
+      <c r="B6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>19330051920058</v>
+      </c>
+      <c r="B7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>19330051920068</v>
+      </c>
+      <c r="B8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8" t="s">
+        <v>84</v>
+      </c>
+      <c r="E8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>19330051920068</v>
+      </c>
+      <c r="B9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>19330051920075</v>
+      </c>
+      <c r="B10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E10" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>19330051920075</v>
+      </c>
+      <c r="B11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11" t="s">
+        <v>87</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>19330051920055</v>
+      </c>
+      <c r="B12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>40</v>
+      </c>
+      <c r="G12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>19330051920059</v>
+      </c>
+      <c r="B13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>40</v>
+      </c>
+      <c r="G13">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/6AEV - Estadisticos 20212.xlsx
+++ b/grupos/6AEV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="98">
   <si>
     <t>Materia</t>
   </si>
@@ -140,15 +140,15 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
-    <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
     <t>Silva Villegas Mario</t>
   </si>
   <si>
@@ -173,142 +173,142 @@
     <t>CRUZ</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>LARA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>VILLAR</t>
+  </si>
+  <si>
+    <t>MONTERO</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>EUSEBIO</t>
+  </si>
+  <si>
+    <t>LUIS ARIEL</t>
+  </si>
+  <si>
+    <t>JONATHAN</t>
+  </si>
+  <si>
+    <t>MARTIN</t>
+  </si>
+  <si>
+    <t>ISAAC ALESSANDRO</t>
+  </si>
+  <si>
+    <t>ALEXIS ARMANDO</t>
+  </si>
+  <si>
+    <t>AGUSTIN</t>
+  </si>
+  <si>
+    <t>SALOMON</t>
+  </si>
+  <si>
+    <t>VICTOR SAUL</t>
+  </si>
+  <si>
+    <t>ALEXIS YAIR</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>IVAN</t>
+  </si>
+  <si>
+    <t>JOSUE YAMIN</t>
+  </si>
+  <si>
+    <t>ARTURO</t>
+  </si>
+  <si>
+    <t>MONSERRAT</t>
+  </si>
+  <si>
+    <t>COSCAHUA</t>
+  </si>
+  <si>
+    <t>ESPINOSA</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>LARA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>GALVEZ</t>
+    <t>MEDRANO</t>
+  </si>
+  <si>
+    <t>TZOYONTLE</t>
+  </si>
+  <si>
+    <t>TZOPITL</t>
   </si>
   <si>
     <t>VALIENTE</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>VILLAR</t>
-  </si>
-  <si>
-    <t>MONTERO</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>EUSEBIO</t>
-  </si>
-  <si>
-    <t>LUIS ARIEL</t>
+    <t>LOZANO</t>
+  </si>
+  <si>
+    <t>ALMA LIZETH</t>
+  </si>
+  <si>
+    <t>YASIEL</t>
   </si>
   <si>
     <t>GERARDO RAUL</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>MARTIN</t>
-  </si>
-  <si>
-    <t>ISAAC ALESSANDRO</t>
-  </si>
-  <si>
-    <t>ALEXIS ARMANDO</t>
-  </si>
-  <si>
-    <t>AGUSTIN</t>
-  </si>
-  <si>
-    <t>SALOMON</t>
-  </si>
-  <si>
-    <t>VICTOR SAUL</t>
-  </si>
-  <si>
-    <t>ALEXIS YAIR</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>JOSUE YAMIN</t>
-  </si>
-  <si>
-    <t>ARTURO</t>
-  </si>
-  <si>
-    <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>COSCAHUA</t>
-  </si>
-  <si>
-    <t>ESPINOSA</t>
-  </si>
-  <si>
-    <t>MEDRANO</t>
-  </si>
-  <si>
-    <t>TZOYONTLE</t>
-  </si>
-  <si>
-    <t>TZOPITL</t>
-  </si>
-  <si>
-    <t>LOZANO</t>
-  </si>
-  <si>
-    <t>ALMA LIZETH</t>
-  </si>
-  <si>
-    <t>YASIEL</t>
   </si>
   <si>
     <t>JOSE DANIEL</t>
@@ -1197,7 +1197,7 @@
         <v>6</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H9">
         <v>-1</v>
@@ -1251,7 +1251,7 @@
         <v>6</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1428,7 +1428,7 @@
         <v>-1</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H12">
         <v>-1</v>
@@ -1482,7 +1482,7 @@
         <v>-1</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1505,7 +1505,7 @@
         <v>6</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H13">
         <v>-1</v>
@@ -1559,7 +1559,7 @@
         <v>6</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1736,7 +1736,7 @@
         <v>-1</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H16">
         <v>-1</v>
@@ -1790,7 +1790,7 @@
         <v>-1</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1813,7 +1813,7 @@
         <v>6</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H17">
         <v>-1</v>
@@ -1867,7 +1867,7 @@
         <v>6</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1967,7 +1967,7 @@
         <v>-1</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H19">
         <v>-1</v>
@@ -2021,7 +2021,7 @@
         <v>-1</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2044,7 +2044,7 @@
         <v>-1</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H20">
         <v>-1</v>
@@ -2098,7 +2098,7 @@
         <v>-1</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2121,7 +2121,7 @@
         <v>7</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H21">
         <v>-1</v>
@@ -2175,7 +2175,7 @@
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2308,7 +2308,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>40</v>
@@ -2317,30 +2317,30 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>21.05</v>
+        <v>26.32</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>6.4</v>
       </c>
       <c r="I2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J2">
-        <v>78.95</v>
+        <v>73.68000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>41</v>
@@ -2349,30 +2349,30 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>26.32</v>
+        <v>57.89</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="I3">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J3">
-        <v>73.68000000000001</v>
+        <v>42.11</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>42</v>
@@ -2381,25 +2381,25 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>57.89</v>
+        <v>63.16</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>42.11</v>
+        <v>36.84</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -2505,7 +2505,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2540,16 +2540,16 @@
         <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2560,16 +2560,16 @@
         <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2580,16 +2580,16 @@
         <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2600,10 +2600,10 @@
         <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -2620,16 +2620,16 @@
         <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2640,33 +2640,33 @@
         <v>50</v>
       </c>
       <c r="C7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>19330051920055</v>
+        <v>19330051920057</v>
       </c>
       <c r="B8" t="s">
         <v>51</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
         <v>40</v>
@@ -2677,39 +2677,39 @@
         <v>19330051920057</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>19330051920057</v>
+        <v>19330051920056</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C10" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2717,19 +2717,19 @@
         <v>19330051920056</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D11" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2737,39 +2737,39 @@
         <v>19330051920056</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D12" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>19330051920056</v>
+        <v>18330051920022</v>
       </c>
       <c r="B13" t="s">
         <v>52</v>
       </c>
       <c r="C13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D13" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2777,76 +2777,76 @@
         <v>18330051920022</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D14" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>18330051920022</v>
+        <v>19330051920058</v>
       </c>
       <c r="B15" t="s">
         <v>53</v>
       </c>
       <c r="C15" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="D15" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E15" t="s">
         <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>18330051920022</v>
+        <v>19330051920059</v>
       </c>
       <c r="B16" t="s">
         <v>53</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>19330051920058</v>
+        <v>19330051920050</v>
       </c>
       <c r="B17" t="s">
         <v>54</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E17" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
         <v>41</v>
@@ -2854,39 +2854,39 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>19330051920058</v>
+        <v>19330051920050</v>
       </c>
       <c r="B18" t="s">
         <v>54</v>
       </c>
       <c r="C18" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F18" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>19330051920059</v>
+        <v>19330051920050</v>
       </c>
       <c r="B19" t="s">
         <v>54</v>
       </c>
       <c r="C19" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D19" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E19" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F19" t="s">
         <v>40</v>
@@ -2897,16 +2897,16 @@
         <v>19330051920050</v>
       </c>
       <c r="B20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D20" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F20" t="s">
         <v>42</v>
@@ -2917,19 +2917,19 @@
         <v>19330051920050</v>
       </c>
       <c r="B21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D21" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E21" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -2937,124 +2937,124 @@
         <v>19330051920050</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D22" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E22" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>19330051920050</v>
+        <v>19330051920064</v>
       </c>
       <c r="B23" t="s">
         <v>55</v>
       </c>
       <c r="C23" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D23" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E23" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F23" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>19330051920050</v>
+        <v>19330051920064</v>
       </c>
       <c r="B24" t="s">
         <v>55</v>
       </c>
       <c r="C24" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D24" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E24" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F24" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>19330051920050</v>
+        <v>19330051920064</v>
       </c>
       <c r="B25" t="s">
         <v>55</v>
       </c>
       <c r="C25" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D25" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E25" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>19330051920064</v>
+        <v>19330051920067</v>
       </c>
       <c r="B26" t="s">
         <v>56</v>
       </c>
       <c r="C26" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D26" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E26" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F26" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>19330051920064</v>
+        <v>19330051920067</v>
       </c>
       <c r="B27" t="s">
         <v>56</v>
       </c>
       <c r="C27" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D27" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E27" t="s">
         <v>5</v>
       </c>
       <c r="F27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>19330051920064</v>
+        <v>19330051920068</v>
       </c>
       <c r="B28" t="s">
         <v>56</v>
@@ -3063,10 +3063,10 @@
         <v>67</v>
       </c>
       <c r="D28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E28" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F28" t="s">
         <v>40</v>
@@ -3074,7 +3074,7 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>19330051920067</v>
+        <v>19330051920074</v>
       </c>
       <c r="B29" t="s">
         <v>57</v>
@@ -3083,18 +3083,18 @@
         <v>68</v>
       </c>
       <c r="D29" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>
       </c>
       <c r="F29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>19330051920067</v>
+        <v>19330051920074</v>
       </c>
       <c r="B30" t="s">
         <v>57</v>
@@ -3103,70 +3103,70 @@
         <v>68</v>
       </c>
       <c r="D30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E30" t="s">
         <v>5</v>
       </c>
       <c r="F30" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>19330051920067</v>
+        <v>18330051920078</v>
       </c>
       <c r="B31" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C31" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D31" t="s">
         <v>83</v>
       </c>
       <c r="E31" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F31" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>19330051920068</v>
+        <v>18330051920078</v>
       </c>
       <c r="B32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C32" t="s">
         <v>69</v>
       </c>
       <c r="D32" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E32" t="s">
         <v>5</v>
       </c>
       <c r="F32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>19330051920068</v>
+        <v>19330051920075</v>
       </c>
       <c r="B33" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C33" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D33" t="s">
         <v>84</v>
       </c>
       <c r="E33" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F33" t="s">
         <v>40</v>
@@ -3174,13 +3174,13 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>19330051920074</v>
+        <v>19330051920081</v>
       </c>
       <c r="B34" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C34" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D34" t="s">
         <v>85</v>
@@ -3189,18 +3189,18 @@
         <v>9</v>
       </c>
       <c r="F34" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>19330051920074</v>
+        <v>19330051920081</v>
       </c>
       <c r="B35" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C35" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D35" t="s">
         <v>85</v>
@@ -3209,18 +3209,18 @@
         <v>5</v>
       </c>
       <c r="F35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>19330051920074</v>
+        <v>19330051920081</v>
       </c>
       <c r="B36" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C36" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D36" t="s">
         <v>85</v>
@@ -3229,167 +3229,7 @@
         <v>10</v>
       </c>
       <c r="F36" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>18330051920078</v>
-      </c>
-      <c r="B37" t="s">
-        <v>59</v>
-      </c>
-      <c r="C37" t="s">
-        <v>71</v>
-      </c>
-      <c r="D37" t="s">
-        <v>86</v>
-      </c>
-      <c r="E37" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" t="s">
         <v>42</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>18330051920078</v>
-      </c>
-      <c r="B38" t="s">
-        <v>59</v>
-      </c>
-      <c r="C38" t="s">
-        <v>71</v>
-      </c>
-      <c r="D38" t="s">
-        <v>86</v>
-      </c>
-      <c r="E38" t="s">
-        <v>5</v>
-      </c>
-      <c r="F38" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>18330051920078</v>
-      </c>
-      <c r="B39" t="s">
-        <v>59</v>
-      </c>
-      <c r="C39" t="s">
-        <v>71</v>
-      </c>
-      <c r="D39" t="s">
-        <v>86</v>
-      </c>
-      <c r="E39" t="s">
-        <v>10</v>
-      </c>
-      <c r="F39" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>19330051920075</v>
-      </c>
-      <c r="B40" t="s">
-        <v>60</v>
-      </c>
-      <c r="C40" t="s">
-        <v>72</v>
-      </c>
-      <c r="D40" t="s">
-        <v>87</v>
-      </c>
-      <c r="E40" t="s">
-        <v>5</v>
-      </c>
-      <c r="F40" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>19330051920075</v>
-      </c>
-      <c r="B41" t="s">
-        <v>60</v>
-      </c>
-      <c r="C41" t="s">
-        <v>72</v>
-      </c>
-      <c r="D41" t="s">
-        <v>87</v>
-      </c>
-      <c r="E41" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>19330051920081</v>
-      </c>
-      <c r="B42" t="s">
-        <v>61</v>
-      </c>
-      <c r="C42" t="s">
-        <v>60</v>
-      </c>
-      <c r="D42" t="s">
-        <v>88</v>
-      </c>
-      <c r="E42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>19330051920081</v>
-      </c>
-      <c r="B43" t="s">
-        <v>61</v>
-      </c>
-      <c r="C43" t="s">
-        <v>60</v>
-      </c>
-      <c r="D43" t="s">
-        <v>88</v>
-      </c>
-      <c r="E43" t="s">
-        <v>5</v>
-      </c>
-      <c r="F43" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>19330051920081</v>
-      </c>
-      <c r="B44" t="s">
-        <v>61</v>
-      </c>
-      <c r="C44" t="s">
-        <v>60</v>
-      </c>
-      <c r="D44" t="s">
-        <v>88</v>
-      </c>
-      <c r="E44" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -3428,13 +3268,13 @@
         <v>19330051920050</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E2">
         <v>6</v>
@@ -3448,10 +3288,10 @@
         <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E3">
         <v>4</v>
@@ -3462,13 +3302,13 @@
         <v>19330051920056</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -3476,16 +3316,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>18330051920022</v>
+        <v>19330051920064</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -3493,16 +3333,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920064</v>
+        <v>19330051920081</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -3510,84 +3350,84 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920067</v>
+        <v>19330051920045</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D7" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920074</v>
+        <v>19330051920057</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>18330051920078</v>
+        <v>18330051920022</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920081</v>
+        <v>19330051920067</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920045</v>
+        <v>19330051920074</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C11" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -3595,16 +3435,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920057</v>
+        <v>18330051920078</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C12" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D12" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -3615,64 +3455,64 @@
         <v>19330051920058</v>
       </c>
       <c r="B13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C13" t="s">
         <v>49</v>
       </c>
       <c r="D13" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920068</v>
+        <v>19330051920059</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C14" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="D14" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920075</v>
+        <v>19330051920068</v>
       </c>
       <c r="B15" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D15" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920055</v>
+        <v>19330051920075</v>
       </c>
       <c r="B16" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D16" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -3680,30 +3520,30 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920059</v>
+        <v>19330051920046</v>
       </c>
       <c r="B17" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="D17" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920046</v>
+        <v>19330051920053</v>
       </c>
       <c r="B18" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C18" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D18" t="s">
         <v>95</v>
@@ -3714,13 +3554,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920053</v>
+        <v>19330051920055</v>
       </c>
       <c r="B19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C19" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D19" t="s">
         <v>96</v>
@@ -3734,10 +3574,10 @@
         <v>19330051920069</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D20" t="s">
         <v>97</v>
@@ -3753,7 +3593,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3791,16 +3631,16 @@
         <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -3814,16 +3654,16 @@
         <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -3834,19 +3674,19 @@
         <v>19330051920057</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -3857,19 +3697,19 @@
         <v>19330051920057</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -3877,22 +3717,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920058</v>
+        <v>18330051920022</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -3900,22 +3740,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920058</v>
+        <v>18330051920022</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -3923,22 +3763,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920068</v>
+        <v>19330051920067</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G8">
         <v>-1</v>
@@ -3946,22 +3786,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920068</v>
+        <v>19330051920067</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G9">
         <v>-1</v>
@@ -3969,22 +3809,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920075</v>
+        <v>19330051920074</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G10">
         <v>-1</v>
@@ -3992,22 +3832,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920075</v>
+        <v>19330051920074</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G11">
         <v>-1</v>
@@ -4015,19 +3855,19 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920055</v>
+        <v>18330051920078</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D12" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
         <v>40</v>
@@ -4038,24 +3878,116 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
+        <v>18330051920078</v>
+      </c>
+      <c r="B13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>19330051920058</v>
+      </c>
+      <c r="B14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" t="s">
+        <v>76</v>
+      </c>
+      <c r="E14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" t="s">
+        <v>40</v>
+      </c>
+      <c r="G14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
         <v>19330051920059</v>
       </c>
-      <c r="B13" t="s">
-        <v>54</v>
-      </c>
-      <c r="C13" t="s">
-        <v>54</v>
-      </c>
-      <c r="D13" t="s">
-        <v>80</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="B15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E15" t="s">
         <v>10</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F15" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>19330051920068</v>
+      </c>
+      <c r="B16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" t="s">
+        <v>81</v>
+      </c>
+      <c r="E16" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" t="s">
         <v>40</v>
       </c>
-      <c r="G13">
+      <c r="G16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>19330051920075</v>
+      </c>
+      <c r="B17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" t="s">
+        <v>84</v>
+      </c>
+      <c r="E17" t="s">
+        <v>5</v>
+      </c>
+      <c r="F17" t="s">
+        <v>40</v>
+      </c>
+      <c r="G17">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/6AEV - Estadisticos 20212.xlsx
+++ b/grupos/6AEV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="98">
   <si>
     <t>Materia</t>
   </si>
@@ -143,18 +143,18 @@
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
+    <t>Silva Villegas Mario</t>
+  </si>
+  <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
-    <t>Silva Villegas Mario</t>
-  </si>
-  <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -197,121 +197,121 @@
     <t>RIVERA</t>
   </si>
   <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>VILLAR</t>
+  </si>
+  <si>
+    <t>MONTERO</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>GALVEZ</t>
+    <t>EUSEBIO</t>
+  </si>
+  <si>
+    <t>LUIS ARIEL</t>
+  </si>
+  <si>
+    <t>MARTIN</t>
+  </si>
+  <si>
+    <t>ISAAC ALESSANDRO</t>
+  </si>
+  <si>
+    <t>ALEXIS ARMANDO</t>
+  </si>
+  <si>
+    <t>SALOMON</t>
+  </si>
+  <si>
+    <t>VICTOR SAUL</t>
+  </si>
+  <si>
+    <t>ALEXIS YAIR</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>IVAN</t>
+  </si>
+  <si>
+    <t>JOSUE YAMIN</t>
+  </si>
+  <si>
+    <t>MONSERRAT</t>
+  </si>
+  <si>
+    <t>COSCAHUA</t>
+  </si>
+  <si>
+    <t>ESPINOSA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MEDRANO</t>
+  </si>
+  <si>
+    <t>TZOYONTLE</t>
+  </si>
+  <si>
+    <t>TZOPITL</t>
+  </si>
+  <si>
+    <t>VALIENTE</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>VILLAR</t>
-  </si>
-  <si>
-    <t>MONTERO</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
+    <t>LOZANO</t>
   </si>
   <si>
     <t>CORTES</t>
   </si>
   <si>
-    <t>EUSEBIO</t>
-  </si>
-  <si>
-    <t>LUIS ARIEL</t>
+    <t>ALMA LIZETH</t>
+  </si>
+  <si>
+    <t>YASIEL</t>
+  </si>
+  <si>
+    <t>GERARDO RAUL</t>
   </si>
   <si>
     <t>JONATHAN</t>
   </si>
   <si>
-    <t>MARTIN</t>
-  </si>
-  <si>
-    <t>ISAAC ALESSANDRO</t>
-  </si>
-  <si>
-    <t>ALEXIS ARMANDO</t>
-  </si>
-  <si>
     <t>AGUSTIN</t>
   </si>
   <si>
-    <t>SALOMON</t>
-  </si>
-  <si>
-    <t>VICTOR SAUL</t>
-  </si>
-  <si>
-    <t>ALEXIS YAIR</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>JOSUE YAMIN</t>
+    <t>JOSE DANIEL</t>
   </si>
   <si>
     <t>ARTURO</t>
-  </si>
-  <si>
-    <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>COSCAHUA</t>
-  </si>
-  <si>
-    <t>ESPINOSA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MEDRANO</t>
-  </si>
-  <si>
-    <t>TZOYONTLE</t>
-  </si>
-  <si>
-    <t>TZOPITL</t>
-  </si>
-  <si>
-    <t>VALIENTE</t>
-  </si>
-  <si>
-    <t>LOZANO</t>
-  </si>
-  <si>
-    <t>ALMA LIZETH</t>
-  </si>
-  <si>
-    <t>YASIEL</t>
-  </si>
-  <si>
-    <t>GERARDO RAUL</t>
-  </si>
-  <si>
-    <t>JOSE DANIEL</t>
   </si>
 </sst>
 </file>
@@ -809,7 +809,7 @@
         <v>8</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G4">
         <v>6</v>
@@ -827,10 +827,10 @@
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -863,7 +863,7 @@
         <v>8</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y4">
         <v>6</v>
@@ -904,10 +904,10 @@
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -943,7 +943,7 @@
         <v>8</v>
       </c>
       <c r="Y5">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -963,10 +963,10 @@
         <v>5</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H6">
         <v>-1</v>
@@ -981,10 +981,10 @@
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1017,10 +1017,10 @@
         <v>5</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1043,7 +1043,7 @@
         <v>-1</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H7">
         <v>-1</v>
@@ -1061,7 +1061,7 @@
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1097,7 +1097,7 @@
         <v>-1</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1135,10 +1135,10 @@
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1171,10 +1171,10 @@
         <v>8</v>
       </c>
       <c r="X8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1212,10 +1212,10 @@
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1248,10 +1248,10 @@
         <v>6</v>
       </c>
       <c r="X9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1274,7 +1274,7 @@
         <v>6</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H10">
         <v>-1</v>
@@ -1289,10 +1289,10 @@
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1328,7 +1328,7 @@
         <v>6</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1336,7 +1336,7 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C11">
         <v>6</v>
@@ -1351,7 +1351,7 @@
         <v>8</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H11">
         <v>-1</v>
@@ -1366,10 +1366,10 @@
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1390,7 +1390,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U11">
         <v>6</v>
@@ -1405,7 +1405,7 @@
         <v>8</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1425,7 +1425,7 @@
         <v>6</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G12">
         <v>6</v>
@@ -1443,10 +1443,10 @@
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1479,10 +1479,10 @@
         <v>6</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1520,10 +1520,10 @@
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1559,7 +1559,7 @@
         <v>6</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1582,7 +1582,7 @@
         <v>6</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H14">
         <v>-1</v>
@@ -1597,10 +1597,10 @@
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1633,10 +1633,10 @@
         <v>8</v>
       </c>
       <c r="X14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1659,7 +1659,7 @@
         <v>6</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H15">
         <v>-1</v>
@@ -1677,7 +1677,7 @@
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1713,7 +1713,7 @@
         <v>6</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1733,7 +1733,7 @@
         <v>6</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G16">
         <v>6</v>
@@ -1751,10 +1751,10 @@
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1787,10 +1787,10 @@
         <v>6</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1828,10 +1828,10 @@
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1864,10 +1864,10 @@
         <v>8</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1905,10 +1905,10 @@
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1944,7 +1944,7 @@
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1964,7 +1964,7 @@
         <v>8</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G19">
         <v>6</v>
@@ -1982,10 +1982,10 @@
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2018,10 +2018,10 @@
         <v>8</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2062,7 +2062,7 @@
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2098,7 +2098,7 @@
         <v>-1</v>
       </c>
       <c r="Y20">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2106,7 +2106,7 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C21">
         <v>9</v>
@@ -2136,10 +2136,10 @@
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2160,7 +2160,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U21">
         <v>9</v>
@@ -2172,10 +2172,10 @@
         <v>8</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2198,7 +2198,7 @@
         <v>-1</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H22">
         <v>-1</v>
@@ -2216,7 +2216,7 @@
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2252,7 +2252,7 @@
         <v>-1</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2317,30 +2317,30 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>26.32</v>
+        <v>36.84</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="I2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J2">
-        <v>73.68000000000001</v>
+        <v>63.16</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>41</v>
@@ -2349,30 +2349,30 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3">
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>52.63</v>
+      </c>
+      <c r="G3">
+        <v>47.37</v>
+      </c>
+      <c r="H3">
+        <v>6.2</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="F3">
-        <v>57.89</v>
-      </c>
-      <c r="G3">
+      <c r="J3">
         <v>0</v>
-      </c>
-      <c r="H3">
-        <v>6.7</v>
-      </c>
-      <c r="I3">
-        <v>8</v>
-      </c>
-      <c r="J3">
-        <v>42.11</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>42</v>
@@ -2381,33 +2381,33 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>63.16</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>21.05</v>
       </c>
       <c r="H4">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="I4">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>36.84</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C5">
         <v>19</v>
@@ -2436,7 +2436,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>43</v>
@@ -2445,30 +2445,30 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>78.95</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>7.9</v>
+      </c>
+      <c r="I6">
         <v>4</v>
       </c>
-      <c r="F6">
-        <v>73.68000000000001</v>
-      </c>
-      <c r="G6">
+      <c r="J6">
         <v>21.05</v>
-      </c>
-      <c r="H6">
-        <v>6.9</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>5.26</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>44</v>
@@ -2477,25 +2477,25 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>78.95</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>7.9</v>
+        <v>7</v>
       </c>
       <c r="I7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J7">
-        <v>21.05</v>
+        <v>15.79</v>
       </c>
     </row>
   </sheetData>
@@ -2505,7 +2505,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2540,36 +2540,36 @@
         <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920045</v>
+        <v>19330051920049</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
         <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2580,50 +2580,50 @@
         <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920049</v>
+        <v>19330051920056</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920049</v>
+        <v>19330051920056</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -2634,10 +2634,10 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920049</v>
+        <v>18330051920022</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C7" t="s">
         <v>62</v>
@@ -2646,21 +2646,21 @@
         <v>72</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>19330051920057</v>
+        <v>19330051920058</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
         <v>73</v>
@@ -2674,33 +2674,33 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920057</v>
+        <v>19330051920050</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>19330051920056</v>
+        <v>19330051920050</v>
       </c>
       <c r="B10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C10" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D10" t="s">
         <v>74</v>
@@ -2709,18 +2709,18 @@
         <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>19330051920056</v>
+        <v>19330051920050</v>
       </c>
       <c r="B11" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C11" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D11" t="s">
         <v>74</v>
@@ -2734,19 +2734,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>19330051920056</v>
+        <v>19330051920050</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D12" t="s">
         <v>74</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
         <v>42</v>
@@ -2754,56 +2754,56 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>18330051920022</v>
+        <v>19330051920050</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C13" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>18330051920022</v>
+        <v>19330051920064</v>
       </c>
       <c r="B14" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s">
         <v>75</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>19330051920058</v>
+        <v>19330051920064</v>
       </c>
       <c r="B15" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="D15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E15" t="s">
         <v>5</v>
@@ -2814,422 +2814,142 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>19330051920059</v>
+        <v>19330051920067</v>
       </c>
       <c r="B16" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="D16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E16" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>19330051920050</v>
+        <v>19330051920068</v>
       </c>
       <c r="B17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C17" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="D17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>19330051920050</v>
+        <v>19330051920074</v>
       </c>
       <c r="B18" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="D18" t="s">
         <v>78</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F18" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>19330051920050</v>
+        <v>18330051920078</v>
       </c>
       <c r="B19" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C19" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="D19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E19" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>19330051920050</v>
+        <v>18330051920078</v>
       </c>
       <c r="B20" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="D20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E20" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>19330051920050</v>
+        <v>19330051920081</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C21" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="D21" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E21" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>19330051920050</v>
+        <v>19330051920081</v>
       </c>
       <c r="B22" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C22" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="D22" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E22" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F22" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>19330051920064</v>
-      </c>
-      <c r="B23" t="s">
-        <v>55</v>
-      </c>
-      <c r="C23" t="s">
-        <v>65</v>
-      </c>
-      <c r="D23" t="s">
-        <v>79</v>
-      </c>
-      <c r="E23" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>19330051920064</v>
-      </c>
-      <c r="B24" t="s">
-        <v>55</v>
-      </c>
-      <c r="C24" t="s">
-        <v>65</v>
-      </c>
-      <c r="D24" t="s">
-        <v>79</v>
-      </c>
-      <c r="E24" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>19330051920064</v>
-      </c>
-      <c r="B25" t="s">
-        <v>55</v>
-      </c>
-      <c r="C25" t="s">
-        <v>65</v>
-      </c>
-      <c r="D25" t="s">
-        <v>79</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>19330051920067</v>
-      </c>
-      <c r="B26" t="s">
-        <v>56</v>
-      </c>
-      <c r="C26" t="s">
-        <v>66</v>
-      </c>
-      <c r="D26" t="s">
-        <v>80</v>
-      </c>
-      <c r="E26" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>19330051920067</v>
-      </c>
-      <c r="B27" t="s">
-        <v>56</v>
-      </c>
-      <c r="C27" t="s">
-        <v>66</v>
-      </c>
-      <c r="D27" t="s">
-        <v>80</v>
-      </c>
-      <c r="E27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>19330051920068</v>
-      </c>
-      <c r="B28" t="s">
-        <v>56</v>
-      </c>
-      <c r="C28" t="s">
-        <v>67</v>
-      </c>
-      <c r="D28" t="s">
-        <v>81</v>
-      </c>
-      <c r="E28" t="s">
-        <v>5</v>
-      </c>
-      <c r="F28" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>19330051920074</v>
-      </c>
-      <c r="B29" t="s">
-        <v>57</v>
-      </c>
-      <c r="C29" t="s">
-        <v>68</v>
-      </c>
-      <c r="D29" t="s">
-        <v>82</v>
-      </c>
-      <c r="E29" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>19330051920074</v>
-      </c>
-      <c r="B30" t="s">
-        <v>57</v>
-      </c>
-      <c r="C30" t="s">
-        <v>68</v>
-      </c>
-      <c r="D30" t="s">
-        <v>82</v>
-      </c>
-      <c r="E30" t="s">
-        <v>5</v>
-      </c>
-      <c r="F30" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>18330051920078</v>
-      </c>
-      <c r="B31" t="s">
-        <v>58</v>
-      </c>
-      <c r="C31" t="s">
-        <v>69</v>
-      </c>
-      <c r="D31" t="s">
-        <v>83</v>
-      </c>
-      <c r="E31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>18330051920078</v>
-      </c>
-      <c r="B32" t="s">
-        <v>58</v>
-      </c>
-      <c r="C32" t="s">
-        <v>69</v>
-      </c>
-      <c r="D32" t="s">
-        <v>83</v>
-      </c>
-      <c r="E32" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>19330051920075</v>
-      </c>
-      <c r="B33" t="s">
-        <v>59</v>
-      </c>
-      <c r="C33" t="s">
-        <v>70</v>
-      </c>
-      <c r="D33" t="s">
-        <v>84</v>
-      </c>
-      <c r="E33" t="s">
-        <v>5</v>
-      </c>
-      <c r="F33" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>19330051920081</v>
-      </c>
-      <c r="B34" t="s">
-        <v>60</v>
-      </c>
-      <c r="C34" t="s">
-        <v>59</v>
-      </c>
-      <c r="D34" t="s">
-        <v>85</v>
-      </c>
-      <c r="E34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>19330051920081</v>
-      </c>
-      <c r="B35" t="s">
-        <v>60</v>
-      </c>
-      <c r="C35" t="s">
-        <v>59</v>
-      </c>
-      <c r="D35" t="s">
-        <v>85</v>
-      </c>
-      <c r="E35" t="s">
-        <v>5</v>
-      </c>
-      <c r="F35" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>19330051920081</v>
-      </c>
-      <c r="B36" t="s">
-        <v>60</v>
-      </c>
-      <c r="C36" t="s">
-        <v>59</v>
-      </c>
-      <c r="D36" t="s">
-        <v>85</v>
-      </c>
-      <c r="E36" t="s">
-        <v>10</v>
-      </c>
-      <c r="F36" t="s">
-        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -3274,10 +2994,10 @@
         <v>56</v>
       </c>
       <c r="D2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3288,13 +3008,13 @@
         <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3305,13 +3025,13 @@
         <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3322,44 +3042,44 @@
         <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920081</v>
+        <v>18330051920078</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920045</v>
+        <v>19330051920081</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="E7">
         <v>2</v>
@@ -3367,19 +3087,19 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920057</v>
+        <v>19330051920045</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -3390,78 +3110,78 @@
         <v>52</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920067</v>
+        <v>19330051920058</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C10" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="D10" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920074</v>
+        <v>19330051920067</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>18330051920078</v>
+        <v>19330051920068</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C12" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D12" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920058</v>
+        <v>19330051920074</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="D13" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -3469,64 +3189,64 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920059</v>
+        <v>19330051920046</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="D14" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920068</v>
+        <v>19330051920053</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="C15" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="D15" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920075</v>
+        <v>19330051920055</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="D16" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920046</v>
+        <v>19330051920057</v>
       </c>
       <c r="B17" t="s">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D17" t="s">
         <v>94</v>
@@ -3537,13 +3257,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920053</v>
+        <v>19330051920059</v>
       </c>
       <c r="B18" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="C18" t="s">
-        <v>91</v>
+        <v>53</v>
       </c>
       <c r="D18" t="s">
         <v>95</v>
@@ -3554,13 +3274,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920055</v>
+        <v>19330051920069</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D19" t="s">
         <v>96</v>
@@ -3571,13 +3291,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920069</v>
+        <v>19330051920075</v>
       </c>
       <c r="B20" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D20" t="s">
         <v>97</v>
@@ -3593,7 +3313,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3625,16 +3345,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920045</v>
+        <v>19330051920058</v>
       </c>
       <c r="B2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" t="s">
         <v>49</v>
       </c>
-      <c r="C2" t="s">
-        <v>61</v>
-      </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -3648,39 +3368,39 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920045</v>
+        <v>19330051920058</v>
       </c>
       <c r="B3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" t="s">
         <v>49</v>
       </c>
-      <c r="C3" t="s">
-        <v>61</v>
-      </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>41</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920057</v>
+        <v>19330051920067</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -3694,39 +3414,39 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920057</v>
+        <v>19330051920067</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>18330051920022</v>
+        <v>19330051920068</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -3740,39 +3460,39 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>18330051920022</v>
+        <v>19330051920068</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
         <v>41</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920067</v>
+        <v>19330051920045</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -3786,39 +3506,39 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920067</v>
+        <v>19330051920055</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
         <v>41</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920074</v>
+        <v>18330051920022</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D10" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
@@ -3838,156 +3558,18 @@
         <v>57</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D11" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>18330051920078</v>
-      </c>
-      <c r="B12" t="s">
-        <v>58</v>
-      </c>
-      <c r="C12" t="s">
-        <v>69</v>
-      </c>
-      <c r="D12" t="s">
-        <v>83</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>40</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>18330051920078</v>
-      </c>
-      <c r="B13" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" t="s">
-        <v>69</v>
-      </c>
-      <c r="D13" t="s">
-        <v>83</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>41</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>19330051920058</v>
-      </c>
-      <c r="B14" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" t="s">
-        <v>76</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>40</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>19330051920059</v>
-      </c>
-      <c r="B15" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" t="s">
-        <v>53</v>
-      </c>
-      <c r="D15" t="s">
-        <v>77</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>42</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>19330051920068</v>
-      </c>
-      <c r="B16" t="s">
-        <v>56</v>
-      </c>
-      <c r="C16" t="s">
-        <v>67</v>
-      </c>
-      <c r="D16" t="s">
-        <v>81</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>40</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>19330051920075</v>
-      </c>
-      <c r="B17" t="s">
-        <v>59</v>
-      </c>
-      <c r="C17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D17" t="s">
-        <v>84</v>
-      </c>
-      <c r="E17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" t="s">
-        <v>40</v>
-      </c>
-      <c r="G17">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/6AEV - Estadisticos 20212.xlsx
+++ b/grupos/6AEV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="98">
   <si>
     <t>Materia</t>
   </si>
@@ -149,12 +149,12 @@
     <t>Silva Villegas Mario</t>
   </si>
   <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -167,10 +167,61 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>LARA</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>VILLAR</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>LUIS ARIEL</t>
+  </si>
+  <si>
+    <t>SALOMON</t>
+  </si>
+  <si>
+    <t>VICTOR SAUL</t>
+  </si>
+  <si>
+    <t>JOSUE YAMIN</t>
+  </si>
+  <si>
+    <t>MONSERRAT</t>
+  </si>
+  <si>
     <t>CHAVEZ</t>
   </si>
   <si>
-    <t>CRUZ</t>
+    <t>COSCAHUA</t>
+  </si>
+  <si>
+    <t>ESPINOSA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
   </si>
   <si>
     <t>GONZALEZ</t>
@@ -182,55 +233,58 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>LARA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
+    <t>MEDRANO</t>
   </si>
   <si>
     <t>REYES</t>
   </si>
   <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
     <t>DE LOS SANTOS</t>
   </si>
   <si>
-    <t>GALVEZ</t>
+    <t>TZOYONTLE</t>
+  </si>
+  <si>
+    <t>TZOPITL</t>
+  </si>
+  <si>
+    <t>VALIENTE</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
   </si>
   <si>
     <t>PAZ</t>
   </si>
   <si>
-    <t>VILLAR</t>
-  </si>
-  <si>
     <t>MONTERO</t>
   </si>
   <si>
     <t>PACHECO</t>
   </si>
   <si>
+    <t>LOZANO</t>
+  </si>
+  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
+    <t>CORTES</t>
   </si>
   <si>
     <t>EUSEBIO</t>
   </si>
   <si>
-    <t>LUIS ARIEL</t>
+    <t>ALMA LIZETH</t>
+  </si>
+  <si>
+    <t>YASIEL</t>
+  </si>
+  <si>
+    <t>GERARDO RAUL</t>
+  </si>
+  <si>
+    <t>JONATHAN</t>
   </si>
   <si>
     <t>MARTIN</t>
@@ -242,10 +296,7 @@
     <t>ALEXIS ARMANDO</t>
   </si>
   <si>
-    <t>SALOMON</t>
-  </si>
-  <si>
-    <t>VICTOR SAUL</t>
+    <t>AGUSTIN</t>
   </si>
   <si>
     <t>ALEXIS YAIR</t>
@@ -254,61 +305,10 @@
     <t>EMMANUEL</t>
   </si>
   <si>
+    <t>JOSE DANIEL</t>
+  </si>
+  <si>
     <t>IVAN</t>
-  </si>
-  <si>
-    <t>JOSUE YAMIN</t>
-  </si>
-  <si>
-    <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>COSCAHUA</t>
-  </si>
-  <si>
-    <t>ESPINOSA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MEDRANO</t>
-  </si>
-  <si>
-    <t>TZOYONTLE</t>
-  </si>
-  <si>
-    <t>TZOPITL</t>
-  </si>
-  <si>
-    <t>VALIENTE</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>LOZANO</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>ALMA LIZETH</t>
-  </si>
-  <si>
-    <t>YASIEL</t>
-  </si>
-  <si>
-    <t>GERARDO RAUL</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>AGUSTIN</t>
-  </si>
-  <si>
-    <t>JOSE DANIEL</t>
   </si>
   <si>
     <t>ARTURO</t>
@@ -797,7 +797,7 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C4">
         <v>6</v>
@@ -815,16 +815,16 @@
         <v>6</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
         <v>6</v>
@@ -851,10 +851,10 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V4">
         <v>8</v>
@@ -892,16 +892,16 @@
         <v>8</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L5">
         <v>8</v>
@@ -928,7 +928,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U5">
         <v>10</v>
@@ -975,10 +975,10 @@
         <v>-1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <v>6</v>
@@ -1031,13 +1031,13 @@
         <v>-1</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F7">
         <v>-1</v>
@@ -1049,13 +1049,13 @@
         <v>-1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
         <v>-1</v>
@@ -1085,13 +1085,13 @@
         <v>-1</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X7">
         <v>-1</v>
@@ -1123,16 +1123,16 @@
         <v>8</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
         <v>9</v>
@@ -1159,10 +1159,10 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V8">
         <v>8</v>
@@ -1200,16 +1200,16 @@
         <v>6</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
         <v>7</v>
@@ -1242,10 +1242,10 @@
         <v>8</v>
       </c>
       <c r="V9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X9">
         <v>7</v>
@@ -1259,10 +1259,10 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D10">
         <v>5</v>
@@ -1277,16 +1277,16 @@
         <v>7</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L10">
         <v>6</v>
@@ -1313,10 +1313,10 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V10">
         <v>5</v>
@@ -1354,16 +1354,16 @@
         <v>6</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L11">
         <v>7</v>
@@ -1393,7 +1393,7 @@
         <v>6</v>
       </c>
       <c r="U11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>8</v>
@@ -1413,7 +1413,7 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C12">
         <v>6</v>
@@ -1431,16 +1431,16 @@
         <v>6</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
         <v>6</v>
@@ -1467,16 +1467,16 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>6</v>
@@ -1490,7 +1490,7 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C13">
         <v>7</v>
@@ -1508,16 +1508,16 @@
         <v>6</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L13">
         <v>6</v>
@@ -1544,16 +1544,16 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U13">
         <v>7</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X13">
         <v>6</v>
@@ -1585,16 +1585,16 @@
         <v>5</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
         <v>9</v>
@@ -1624,7 +1624,7 @@
         <v>7</v>
       </c>
       <c r="U14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>8</v>
@@ -1668,10 +1668,10 @@
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L15">
         <v>-1</v>
@@ -1721,7 +1721,7 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C16">
         <v>6</v>
@@ -1739,16 +1739,16 @@
         <v>6</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L16">
         <v>6</v>
@@ -1775,16 +1775,16 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U16">
         <v>6</v>
       </c>
       <c r="V16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X16">
         <v>6</v>
@@ -1798,7 +1798,7 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C17">
         <v>8</v>
@@ -1816,16 +1816,16 @@
         <v>6</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
         <v>7</v>
@@ -1852,7 +1852,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U17">
         <v>8</v>
@@ -1893,16 +1893,16 @@
         <v>7</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U18">
         <v>10</v>
@@ -1952,7 +1952,7 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C19">
         <v>9</v>
@@ -1970,16 +1970,16 @@
         <v>6</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
         <v>9</v>
@@ -2006,10 +2006,10 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V19">
         <v>8</v>
@@ -2029,7 +2029,7 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C20">
         <v>7</v>
@@ -2047,16 +2047,16 @@
         <v>6</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L20">
         <v>-1</v>
@@ -2083,16 +2083,16 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U20">
         <v>7</v>
       </c>
       <c r="V20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X20">
         <v>-1</v>
@@ -2124,16 +2124,16 @@
         <v>7</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L21">
         <v>8</v>
@@ -2160,10 +2160,10 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V21">
         <v>8</v>
@@ -2183,7 +2183,7 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C22">
         <v>10</v>
@@ -2204,13 +2204,13 @@
         <v>-1</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L22">
         <v>-1</v>
@@ -2237,10 +2237,10 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V22">
         <v>5</v>
@@ -2317,25 +2317,25 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F2">
+        <v>47.37</v>
+      </c>
+      <c r="G2">
         <v>36.84</v>
       </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
       <c r="H2">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="I2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>63.16</v>
+        <v>15.79</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -2381,25 +2381,25 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>73.68000000000001</v>
+        <v>68.42</v>
       </c>
       <c r="G4">
-        <v>21.05</v>
+        <v>31.58</v>
       </c>
       <c r="H4">
         <v>6.9</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -2413,30 +2413,30 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>73.68000000000001</v>
+        <v>68.42</v>
       </c>
       <c r="G5">
-        <v>21.05</v>
+        <v>31.58</v>
       </c>
       <c r="H5">
         <v>6.9</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>43</v>
@@ -2445,30 +2445,30 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>78.95</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>7</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>21.05</v>
+        <v>15.79</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>44</v>
@@ -2477,25 +2477,25 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>84.20999999999999</v>
+        <v>89.47</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="I7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J7">
-        <v>15.79</v>
+        <v>10.53</v>
       </c>
     </row>
   </sheetData>
@@ -2505,7 +2505,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2534,22 +2534,22 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>19330051920045</v>
+        <v>19330051920049</v>
       </c>
       <c r="B2" t="s">
         <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2557,93 +2557,93 @@
         <v>19330051920049</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920049</v>
+        <v>19330051920050</v>
       </c>
       <c r="B4" t="s">
         <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920056</v>
+        <v>19330051920050</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" t="s">
         <v>60</v>
       </c>
-      <c r="D5" t="s">
-        <v>71</v>
-      </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920056</v>
+        <v>19330051920064</v>
       </c>
       <c r="B6" t="s">
         <v>51</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D6" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>18330051920022</v>
+        <v>19330051920064</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E7" t="s">
         <v>5</v>
@@ -2654,302 +2654,42 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>19330051920058</v>
+        <v>18330051920078</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D8" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920050</v>
+        <v>19330051920081</v>
       </c>
       <c r="B9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D9" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>19330051920050</v>
-      </c>
-      <c r="B10" t="s">
-        <v>54</v>
-      </c>
-      <c r="C10" t="s">
-        <v>56</v>
-      </c>
-      <c r="D10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
         <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>19330051920050</v>
-      </c>
-      <c r="B11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D11" t="s">
-        <v>74</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>19330051920050</v>
-      </c>
-      <c r="B12" t="s">
-        <v>54</v>
-      </c>
-      <c r="C12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D12" t="s">
-        <v>74</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>19330051920050</v>
-      </c>
-      <c r="B13" t="s">
-        <v>54</v>
-      </c>
-      <c r="C13" t="s">
-        <v>56</v>
-      </c>
-      <c r="D13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>19330051920064</v>
-      </c>
-      <c r="B14" t="s">
-        <v>55</v>
-      </c>
-      <c r="C14" t="s">
-        <v>63</v>
-      </c>
-      <c r="D14" t="s">
-        <v>75</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>19330051920064</v>
-      </c>
-      <c r="B15" t="s">
-        <v>55</v>
-      </c>
-      <c r="C15" t="s">
-        <v>63</v>
-      </c>
-      <c r="D15" t="s">
-        <v>75</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>19330051920067</v>
-      </c>
-      <c r="B16" t="s">
-        <v>56</v>
-      </c>
-      <c r="C16" t="s">
-        <v>64</v>
-      </c>
-      <c r="D16" t="s">
-        <v>76</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>19330051920068</v>
-      </c>
-      <c r="B17" t="s">
-        <v>56</v>
-      </c>
-      <c r="C17" t="s">
-        <v>65</v>
-      </c>
-      <c r="D17" t="s">
-        <v>77</v>
-      </c>
-      <c r="E17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>19330051920074</v>
-      </c>
-      <c r="B18" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" t="s">
-        <v>66</v>
-      </c>
-      <c r="D18" t="s">
-        <v>78</v>
-      </c>
-      <c r="E18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>18330051920078</v>
-      </c>
-      <c r="B19" t="s">
-        <v>58</v>
-      </c>
-      <c r="C19" t="s">
-        <v>67</v>
-      </c>
-      <c r="D19" t="s">
-        <v>79</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>18330051920078</v>
-      </c>
-      <c r="B20" t="s">
-        <v>58</v>
-      </c>
-      <c r="C20" t="s">
-        <v>67</v>
-      </c>
-      <c r="D20" t="s">
-        <v>79</v>
-      </c>
-      <c r="E20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>19330051920081</v>
-      </c>
-      <c r="B21" t="s">
-        <v>59</v>
-      </c>
-      <c r="C21" t="s">
-        <v>68</v>
-      </c>
-      <c r="D21" t="s">
-        <v>80</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>19330051920081</v>
-      </c>
-      <c r="B22" t="s">
-        <v>59</v>
-      </c>
-      <c r="C22" t="s">
-        <v>68</v>
-      </c>
-      <c r="D22" t="s">
-        <v>80</v>
-      </c>
-      <c r="E22" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -2985,33 +2725,33 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920050</v>
+        <v>19330051920049</v>
       </c>
       <c r="B2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" t="s">
         <v>54</v>
       </c>
-      <c r="C2" t="s">
-        <v>56</v>
-      </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920049</v>
+        <v>19330051920050</v>
       </c>
       <c r="B3" t="s">
         <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -3019,16 +2759,16 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920056</v>
+        <v>19330051920064</v>
       </c>
       <c r="B4" t="s">
         <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D4" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -3036,166 +2776,166 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920064</v>
+        <v>18330051920078</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D5" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>18330051920078</v>
+        <v>19330051920081</v>
       </c>
       <c r="B6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" t="s">
         <v>58</v>
       </c>
-      <c r="C6" t="s">
-        <v>67</v>
-      </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920081</v>
+        <v>19330051920045</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920045</v>
+        <v>19330051920046</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>18330051920022</v>
+        <v>19330051920053</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="D9" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920058</v>
+        <v>19330051920055</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="D10" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920067</v>
+        <v>19330051920057</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D11" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920068</v>
+        <v>19330051920056</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920074</v>
+        <v>18330051920022</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="D13" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920046</v>
+        <v>19330051920058</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="C14" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="D14" t="s">
         <v>91</v>
@@ -3206,13 +2946,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920053</v>
+        <v>19330051920059</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="D15" t="s">
         <v>92</v>
@@ -3223,13 +2963,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920055</v>
+        <v>19330051920067</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="C16" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D16" t="s">
         <v>93</v>
@@ -3240,13 +2980,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920057</v>
+        <v>19330051920068</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C17" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D17" t="s">
         <v>94</v>
@@ -3257,13 +2997,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920059</v>
+        <v>19330051920069</v>
       </c>
       <c r="B18" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="D18" t="s">
         <v>95</v>
@@ -3274,13 +3014,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920069</v>
+        <v>19330051920074</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C19" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D19" t="s">
         <v>96</v>
@@ -3294,10 +3034,10 @@
         <v>19330051920075</v>
       </c>
       <c r="B20" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C20" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D20" t="s">
         <v>97</v>
@@ -3313,7 +3053,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3345,45 +3085,45 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920058</v>
+        <v>19330051920056</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920058</v>
+        <v>19330051920056</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -3391,16 +3131,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920067</v>
+        <v>19330051920058</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
         <v>64</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -3409,21 +3149,21 @@
         <v>40</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920067</v>
+        <v>19330051920058</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
         <v>64</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -3440,13 +3180,13 @@
         <v>19330051920068</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -3455,7 +3195,7 @@
         <v>40</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -3463,13 +3203,13 @@
         <v>19330051920068</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -3486,13 +3226,13 @@
         <v>19330051920045</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -3501,7 +3241,7 @@
         <v>40</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -3509,13 +3249,13 @@
         <v>19330051920055</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D9" t="s">
         <v>87</v>
-      </c>
-      <c r="D9" t="s">
-        <v>93</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -3532,13 +3272,13 @@
         <v>18330051920022</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="D10" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
@@ -3547,30 +3287,7 @@
         <v>40</v>
       </c>
       <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>19330051920074</v>
-      </c>
-      <c r="B11" t="s">
-        <v>57</v>
-      </c>
-      <c r="C11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D11" t="s">
-        <v>78</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>40</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/6AEV - Estadisticos 20212.xlsx
+++ b/grupos/6AEV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="98">
   <si>
     <t>Materia</t>
   </si>
@@ -176,142 +176,142 @@
     <t>LARA</t>
   </si>
   <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>VILLAR</t>
+  </si>
+  <si>
+    <t>LUIS ARIEL</t>
+  </si>
+  <si>
+    <t>SALOMON</t>
+  </si>
+  <si>
+    <t>VICTOR SAUL</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>COSCAHUA</t>
+  </si>
+  <si>
+    <t>ESPINOSA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MEDRANO</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
     <t>RIVERA</t>
   </si>
   <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>VILLAR</t>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>TZOYONTLE</t>
+  </si>
+  <si>
+    <t>TZOPITL</t>
+  </si>
+  <si>
+    <t>VALIENTE</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>MONTERO</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>LOZANO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
   </si>
   <si>
     <t>SARMIENTO</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>LUIS ARIEL</t>
-  </si>
-  <si>
-    <t>SALOMON</t>
-  </si>
-  <si>
-    <t>VICTOR SAUL</t>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>EUSEBIO</t>
+  </si>
+  <si>
+    <t>ALMA LIZETH</t>
+  </si>
+  <si>
+    <t>YASIEL</t>
+  </si>
+  <si>
+    <t>GERARDO RAUL</t>
+  </si>
+  <si>
+    <t>JONATHAN</t>
+  </si>
+  <si>
+    <t>MARTIN</t>
+  </si>
+  <si>
+    <t>ISAAC ALESSANDRO</t>
+  </si>
+  <si>
+    <t>ALEXIS ARMANDO</t>
+  </si>
+  <si>
+    <t>AGUSTIN</t>
+  </si>
+  <si>
+    <t>ALEXIS YAIR</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>JOSE DANIEL</t>
+  </si>
+  <si>
+    <t>IVAN</t>
   </si>
   <si>
     <t>JOSUE YAMIN</t>
   </si>
   <si>
+    <t>ARTURO</t>
+  </si>
+  <si>
     <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>COSCAHUA</t>
-  </si>
-  <si>
-    <t>ESPINOSA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MEDRANO</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>TZOYONTLE</t>
-  </si>
-  <si>
-    <t>TZOPITL</t>
-  </si>
-  <si>
-    <t>VALIENTE</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>MONTERO</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>LOZANO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>EUSEBIO</t>
-  </si>
-  <si>
-    <t>ALMA LIZETH</t>
-  </si>
-  <si>
-    <t>YASIEL</t>
-  </si>
-  <si>
-    <t>GERARDO RAUL</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>MARTIN</t>
-  </si>
-  <si>
-    <t>ISAAC ALESSANDRO</t>
-  </si>
-  <si>
-    <t>ALEXIS ARMANDO</t>
-  </si>
-  <si>
-    <t>AGUSTIN</t>
-  </si>
-  <si>
-    <t>ALEXIS YAIR</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>JOSE DANIEL</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>ARTURO</t>
   </si>
 </sst>
 </file>
@@ -845,7 +845,7 @@
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S4">
         <v>-1</v>
@@ -922,7 +922,7 @@
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -940,7 +940,7 @@
         <v>9</v>
       </c>
       <c r="X5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y5">
         <v>7</v>
@@ -999,7 +999,7 @@
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S6">
         <v>-1</v>
@@ -1017,7 +1017,7 @@
         <v>5</v>
       </c>
       <c r="X6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y6">
         <v>5</v>
@@ -1040,7 +1040,7 @@
         <v>5</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -1058,7 +1058,7 @@
         <v>6</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M7">
         <v>5</v>
@@ -1076,7 +1076,7 @@
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -1094,7 +1094,7 @@
         <v>5</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y7">
         <v>5</v>
@@ -1153,7 +1153,7 @@
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S8">
         <v>-1</v>
@@ -1230,7 +1230,7 @@
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -1307,7 +1307,7 @@
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -1384,7 +1384,7 @@
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S11">
         <v>-1</v>
@@ -1402,7 +1402,7 @@
         <v>8</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y11">
         <v>6</v>
@@ -1461,7 +1461,7 @@
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S12">
         <v>-1</v>
@@ -1538,7 +1538,7 @@
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -1615,7 +1615,7 @@
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -1674,7 +1674,7 @@
         <v>5</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M15">
         <v>5</v>
@@ -1692,7 +1692,7 @@
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S15">
         <v>-1</v>
@@ -1710,7 +1710,7 @@
         <v>5</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y15">
         <v>5</v>
@@ -1769,7 +1769,7 @@
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -1846,7 +1846,7 @@
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -1923,7 +1923,7 @@
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S18">
         <v>-1</v>
@@ -2000,7 +2000,7 @@
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -2018,7 +2018,7 @@
         <v>8</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y19">
         <v>7</v>
@@ -2041,7 +2041,7 @@
         <v>6</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G20">
         <v>6</v>
@@ -2059,7 +2059,7 @@
         <v>8</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
         <v>5</v>
@@ -2077,7 +2077,7 @@
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S20">
         <v>-1</v>
@@ -2095,7 +2095,7 @@
         <v>7</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y20">
         <v>5</v>
@@ -2154,7 +2154,7 @@
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S21">
         <v>-1</v>
@@ -2195,7 +2195,7 @@
         <v>5</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G22">
         <v>5</v>
@@ -2213,7 +2213,7 @@
         <v>5</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
         <v>5</v>
@@ -2231,7 +2231,7 @@
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S22">
         <v>-1</v>
@@ -2249,7 +2249,7 @@
         <v>5</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y22">
         <v>5</v>
@@ -2445,25 +2445,25 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>78.95</v>
+      </c>
+      <c r="G6">
+        <v>21.05</v>
+      </c>
+      <c r="H6">
+        <v>6.6</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>84.20999999999999</v>
-      </c>
-      <c r="G6">
+      <c r="J6">
         <v>0</v>
-      </c>
-      <c r="H6">
-        <v>7</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
-      <c r="J6">
-        <v>15.79</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -2505,7 +2505,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2540,10 +2540,10 @@
         <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -2560,10 +2560,10 @@
         <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
@@ -2580,36 +2580,36 @@
         <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920050</v>
+        <v>19330051920064</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2620,76 +2620,16 @@
         <v>51</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>19330051920064</v>
-      </c>
-      <c r="B7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C7" t="s">
-        <v>56</v>
-      </c>
-      <c r="D7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>18330051920078</v>
-      </c>
-      <c r="B8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" t="s">
-        <v>57</v>
-      </c>
-      <c r="D8" t="s">
-        <v>62</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>19330051920081</v>
-      </c>
-      <c r="B9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C9" t="s">
-        <v>58</v>
-      </c>
-      <c r="D9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -2731,10 +2671,10 @@
         <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -2742,16 +2682,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920050</v>
+        <v>19330051920064</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -2759,64 +2699,64 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920064</v>
+        <v>19330051920050</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" t="s">
         <v>56</v>
       </c>
-      <c r="D4" t="s">
-        <v>61</v>
-      </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>18330051920078</v>
+        <v>19330051920045</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920081</v>
+        <v>19330051920046</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920045</v>
+        <v>19330051920053</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
         <v>84</v>
@@ -2827,13 +2767,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920046</v>
+        <v>19330051920055</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D8" t="s">
         <v>85</v>
@@ -2844,13 +2784,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920053</v>
+        <v>19330051920057</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D9" t="s">
         <v>86</v>
@@ -2861,13 +2801,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920055</v>
+        <v>19330051920056</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D10" t="s">
         <v>87</v>
@@ -2878,13 +2818,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920057</v>
+        <v>18330051920022</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D11" t="s">
         <v>88</v>
@@ -2895,13 +2835,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920056</v>
+        <v>19330051920058</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s">
         <v>89</v>
@@ -2912,13 +2852,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>18330051920022</v>
+        <v>19330051920059</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="D13" t="s">
         <v>90</v>
@@ -2929,13 +2869,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920058</v>
+        <v>19330051920067</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="D14" t="s">
         <v>91</v>
@@ -2946,13 +2886,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920059</v>
+        <v>19330051920068</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C15" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="D15" t="s">
         <v>92</v>
@@ -2963,13 +2903,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920067</v>
+        <v>19330051920069</v>
       </c>
       <c r="B16" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D16" t="s">
         <v>93</v>
@@ -2980,13 +2920,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920068</v>
+        <v>19330051920074</v>
       </c>
       <c r="B17" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D17" t="s">
         <v>94</v>
@@ -2997,13 +2937,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920069</v>
+        <v>18330051920078</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D18" t="s">
         <v>95</v>
@@ -3014,13 +2954,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920074</v>
+        <v>19330051920075</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D19" t="s">
         <v>96</v>
@@ -3031,13 +2971,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920075</v>
+        <v>19330051920081</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="C20" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="D20" t="s">
         <v>97</v>
@@ -3088,13 +3028,13 @@
         <v>19330051920056</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -3111,13 +3051,13 @@
         <v>19330051920056</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -3134,13 +3074,13 @@
         <v>19330051920058</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -3157,13 +3097,13 @@
         <v>19330051920058</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -3180,13 +3120,13 @@
         <v>19330051920068</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -3203,13 +3143,13 @@
         <v>19330051920068</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -3226,13 +3166,13 @@
         <v>19330051920045</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -3249,13 +3189,13 @@
         <v>19330051920055</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -3272,13 +3212,13 @@
         <v>18330051920022</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>

--- a/grupos/6AEV - Estadisticos 20212.xlsx
+++ b/grupos/6AEV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="98">
   <si>
     <t>Materia</t>
   </si>
@@ -140,18 +140,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
+    <t>Silva Villegas Mario</t>
+  </si>
+  <si>
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
-    <t>Silva Villegas Mario</t>
-  </si>
-  <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
@@ -167,130 +167,130 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>COSCAHUA</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
+    <t>ESPINOSA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
     <t>LARA</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MEDRANO</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>TZOYONTLE</t>
+  </si>
+  <si>
     <t>GALVEZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
+    <t>TZOPITL</t>
+  </si>
+  <si>
+    <t>VALIENTE</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>PAZ</t>
   </si>
   <si>
     <t>VILLAR</t>
   </si>
   <si>
+    <t>MONTERO</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>LOZANO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>EUSEBIO</t>
+  </si>
+  <si>
+    <t>ALMA LIZETH</t>
+  </si>
+  <si>
     <t>LUIS ARIEL</t>
   </si>
   <si>
+    <t>YASIEL</t>
+  </si>
+  <si>
+    <t>GERARDO RAUL</t>
+  </si>
+  <si>
+    <t>JONATHAN</t>
+  </si>
+  <si>
+    <t>MARTIN</t>
+  </si>
+  <si>
+    <t>ISAAC ALESSANDRO</t>
+  </si>
+  <si>
+    <t>ALEXIS ARMANDO</t>
+  </si>
+  <si>
+    <t>AGUSTIN</t>
+  </si>
+  <si>
     <t>SALOMON</t>
   </si>
   <si>
     <t>VICTOR SAUL</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>COSCAHUA</t>
-  </si>
-  <si>
-    <t>ESPINOSA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MEDRANO</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>TZOYONTLE</t>
-  </si>
-  <si>
-    <t>TZOPITL</t>
-  </si>
-  <si>
-    <t>VALIENTE</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>MONTERO</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>LOZANO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>EUSEBIO</t>
-  </si>
-  <si>
-    <t>ALMA LIZETH</t>
-  </si>
-  <si>
-    <t>YASIEL</t>
-  </si>
-  <si>
-    <t>GERARDO RAUL</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>MARTIN</t>
-  </si>
-  <si>
-    <t>ISAAC ALESSANDRO</t>
-  </si>
-  <si>
-    <t>ALEXIS ARMANDO</t>
-  </si>
-  <si>
-    <t>AGUSTIN</t>
   </si>
   <si>
     <t>ALEXIS YAIR</t>
@@ -833,40 +833,40 @@
         <v>6</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R4">
         <v>7</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U4">
         <v>8</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X4">
         <v>6</v>
       </c>
       <c r="Y4">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -910,25 +910,25 @@
         <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
         <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U5">
         <v>10</v>
@@ -943,7 +943,7 @@
         <v>9</v>
       </c>
       <c r="Y5">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -951,10 +951,10 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -969,10 +969,10 @@
         <v>5</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J6">
         <v>5</v>
@@ -987,28 +987,28 @@
         <v>5</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R6">
         <v>5</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V6">
         <v>5</v>
@@ -1028,7 +1028,7 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1046,7 +1046,7 @@
         <v>5</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I7">
         <v>6</v>
@@ -1064,40 +1064,40 @@
         <v>5</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
         <v>6</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X7">
         <v>6</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1141,22 +1141,22 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
         <v>8</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
         <v>8</v>
@@ -1218,22 +1218,22 @@
         <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
         <v>8</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T9">
         <v>6</v>
@@ -1251,7 +1251,7 @@
         <v>7</v>
       </c>
       <c r="Y9">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1295,22 +1295,22 @@
         <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
         <v>7</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T10">
         <v>6</v>
@@ -1319,10 +1319,10 @@
         <v>7</v>
       </c>
       <c r="V10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X10">
         <v>6</v>
@@ -1372,34 +1372,34 @@
         <v>6</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
         <v>6</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T11">
         <v>6</v>
       </c>
       <c r="U11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X11">
         <v>7</v>
@@ -1449,25 +1449,25 @@
         <v>7</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R12">
         <v>6</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U12">
         <v>7</v>
@@ -1526,40 +1526,40 @@
         <v>5</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R13">
         <v>6</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X13">
         <v>6</v>
       </c>
       <c r="Y13">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1603,40 +1603,40 @@
         <v>7</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R14">
         <v>8</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V14">
         <v>8</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X14">
         <v>8</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1644,10 +1644,10 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D15">
         <v>5</v>
@@ -1662,10 +1662,10 @@
         <v>5</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J15">
         <v>5</v>
@@ -1680,28 +1680,28 @@
         <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R15">
         <v>5</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V15">
         <v>5</v>
@@ -1757,25 +1757,25 @@
         <v>5</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R16">
         <v>7</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U16">
         <v>6</v>
@@ -1790,7 +1790,7 @@
         <v>6</v>
       </c>
       <c r="Y16">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1834,40 +1834,40 @@
         <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>9</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U17">
         <v>8</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X17">
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1911,22 +1911,22 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
         <v>8</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>8</v>
@@ -1988,25 +1988,25 @@
         <v>7</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
         <v>6</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U19">
         <v>8</v>
@@ -2065,22 +2065,22 @@
         <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>5</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T20">
         <v>5</v>
@@ -2089,16 +2089,16 @@
         <v>7</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X20">
         <v>5</v>
       </c>
       <c r="Y20">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2142,28 +2142,28 @@
         <v>8</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
         <v>9</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
         <v>7</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V21">
         <v>8</v>
@@ -2201,7 +2201,7 @@
         <v>5</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I22">
         <v>6</v>
@@ -2219,28 +2219,28 @@
         <v>5</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R22">
         <v>5</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T22">
         <v>5</v>
       </c>
       <c r="U22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V22">
         <v>5</v>
@@ -2308,7 +2308,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>40</v>
@@ -2317,30 +2317,30 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>47.37</v>
+        <v>78.95</v>
       </c>
       <c r="G2">
-        <v>36.84</v>
+        <v>21.05</v>
       </c>
       <c r="H2">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>15.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>41</v>
@@ -2349,19 +2349,19 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>52.63</v>
+        <v>78.95</v>
       </c>
       <c r="G3">
-        <v>47.37</v>
+        <v>21.05</v>
       </c>
       <c r="H3">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2381,19 +2381,19 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>68.42</v>
+        <v>78.95</v>
       </c>
       <c r="G4">
-        <v>31.58</v>
+        <v>21.05</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2413,19 +2413,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>68.42</v>
+        <v>78.95</v>
       </c>
       <c r="G5">
-        <v>31.58</v>
+        <v>21.05</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2436,7 +2436,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>43</v>
@@ -2445,19 +2445,19 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>78.95</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="G6">
-        <v>21.05</v>
+        <v>15.79</v>
       </c>
       <c r="H6">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2480,22 +2480,22 @@
         <v>17</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7">
         <v>89.47</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>10.53</v>
       </c>
       <c r="H7">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="I7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>10.53</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2505,7 +2505,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2530,106 +2530,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>19330051920049</v>
-      </c>
-      <c r="B2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>19330051920049</v>
-      </c>
-      <c r="B3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>19330051920050</v>
-      </c>
-      <c r="B4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>19330051920064</v>
-      </c>
-      <c r="B5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>19330051920064</v>
-      </c>
-      <c r="B6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" t="s">
-        <v>57</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -2665,64 +2565,64 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920049</v>
+        <v>19330051920045</v>
       </c>
       <c r="B2" t="s">
         <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920064</v>
+        <v>19330051920046</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920050</v>
+        <v>19330051920049</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920045</v>
+        <v>19330051920053</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D5" t="s">
         <v>82</v>
@@ -2733,13 +2633,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920046</v>
+        <v>19330051920055</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
         <v>83</v>
@@ -2750,13 +2650,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920053</v>
+        <v>19330051920057</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
         <v>84</v>
@@ -2767,13 +2667,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920055</v>
+        <v>19330051920056</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
         <v>85</v>
@@ -2784,13 +2684,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920057</v>
+        <v>18330051920022</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D9" t="s">
         <v>86</v>
@@ -2801,13 +2701,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920056</v>
+        <v>19330051920058</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="D10" t="s">
         <v>87</v>
@@ -2818,13 +2718,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>18330051920022</v>
+        <v>19330051920059</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="D11" t="s">
         <v>88</v>
@@ -2835,13 +2735,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920058</v>
+        <v>19330051920050</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D12" t="s">
         <v>89</v>
@@ -2852,13 +2752,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920059</v>
+        <v>19330051920064</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C13" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D13" t="s">
         <v>90</v>
@@ -2872,10 +2772,10 @@
         <v>19330051920067</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C14" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D14" t="s">
         <v>91</v>
@@ -2889,10 +2789,10 @@
         <v>19330051920068</v>
       </c>
       <c r="B15" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C15" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D15" t="s">
         <v>92</v>
@@ -2906,10 +2806,10 @@
         <v>19330051920069</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C16" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D16" t="s">
         <v>93</v>
@@ -2923,10 +2823,10 @@
         <v>19330051920074</v>
       </c>
       <c r="B17" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D17" t="s">
         <v>94</v>
@@ -2940,10 +2840,10 @@
         <v>18330051920078</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C18" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D18" t="s">
         <v>95</v>
@@ -2957,10 +2857,10 @@
         <v>19330051920075</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C19" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D19" t="s">
         <v>96</v>
@@ -2974,10 +2874,10 @@
         <v>19330051920081</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C20" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D20" t="s">
         <v>97</v>
@@ -2993,7 +2893,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3025,16 +2925,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920056</v>
+        <v>19330051920067</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -3048,16 +2948,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920056</v>
+        <v>19330051920067</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -3071,22 +2971,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920058</v>
+        <v>18330051920078</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -3094,139 +2994,24 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920058</v>
+        <v>18330051920078</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>19330051920068</v>
-      </c>
-      <c r="B6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D6" t="s">
-        <v>92</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>19330051920068</v>
-      </c>
-      <c r="B7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C7" t="s">
-        <v>77</v>
-      </c>
-      <c r="D7" t="s">
-        <v>92</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>41</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>19330051920045</v>
-      </c>
-      <c r="B8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C8" t="s">
-        <v>70</v>
-      </c>
-      <c r="D8" t="s">
-        <v>82</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>19330051920055</v>
-      </c>
-      <c r="B9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C9" t="s">
-        <v>73</v>
-      </c>
-      <c r="D9" t="s">
-        <v>85</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>41</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>18330051920022</v>
-      </c>
-      <c r="B10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" t="s">
-        <v>75</v>
-      </c>
-      <c r="D10" t="s">
-        <v>88</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>40</v>
-      </c>
-      <c r="G10">
         <v>5</v>
       </c>
     </row>
